--- a/Scout/crk-vs-waukee-091126.xlsx
+++ b/Scout/crk-vs-waukee-091126.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R99792932f5fc4a8d"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Rbe6d9bfc8b434bec"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -118,6 +130,9 @@
     <t>N</t>
   </si>
   <si>
+    <t>G GUN</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -127,6 +142,9 @@
     <t>Penalty</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>Run</t>
   </si>
   <si>
@@ -142,6 +160,12 @@
     <t>Incomplete</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>GUN</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -175,6 +199,9 @@
     <t>O</t>
   </si>
   <si>
+    <t>G I DOT UNDER</t>
+  </si>
+  <si>
     <t>SPLIT</t>
   </si>
   <si>
@@ -184,6 +211,9 @@
     <t>C</t>
   </si>
   <si>
+    <t>G DOT</t>
+  </si>
+  <si>
     <t>PRO</t>
   </si>
   <si>
@@ -250,6 +280,9 @@
     <t>ZONE READ</t>
   </si>
   <si>
+    <t>K DOT</t>
+  </si>
+  <si>
     <t>BASE POWER</t>
   </si>
   <si>
@@ -265,6 +298,9 @@
     <t>SMASH</t>
   </si>
   <si>
+    <t>GUN EVEN</t>
+  </si>
+  <si>
     <t>FAR</t>
   </si>
   <si>
@@ -278,6 +314,9 @@
   </si>
   <si>
     <t>Scramble</t>
+  </si>
+  <si>
+    <t>GUN STACK K</t>
   </si>
   <si>
     <t>TOWARD</t>
@@ -353,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y155"/>
+  <dimension ref="A1:AC155"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -431,6 +470,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -440,7 +491,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -451,7 +502,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -473,19 +524,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>-40</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -508,19 +559,19 @@
         <v>-31</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <v>6</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -531,16 +582,19 @@
       <c r="O6">
         <v>2</v>
       </c>
-      <c r="R6" t="s">
-        <v>35</v>
-      </c>
-      <c r="S6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U6" t="s">
-        <v>35</v>
-      </c>
-      <c r="X6">
+      <c r="P6" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" t="s">
+        <v>40</v>
+      </c>
+      <c r="X6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -552,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -564,21 +618,24 @@
         <v>-37</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
-      </c>
-      <c r="R7" t="s">
-        <v>31</v>
-      </c>
-      <c r="X7">
+        <v>38</v>
+      </c>
+      <c r="P7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -590,7 +647,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -602,33 +659,36 @@
         <v>-42</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J8">
         <v>-3</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L8">
         <v>7</v>
       </c>
       <c r="M8" t="s">
-        <v>41</v>
-      </c>
-      <c r="R8" t="s">
-        <v>31</v>
-      </c>
-      <c r="U8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X8">
+        <v>47</v>
+      </c>
+      <c r="P8" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -640,7 +700,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -652,19 +712,19 @@
         <v>-39</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -675,16 +735,19 @@
       <c r="O9">
         <v>3</v>
       </c>
-      <c r="R9" t="s">
-        <v>31</v>
-      </c>
-      <c r="U9" t="s">
-        <v>35</v>
-      </c>
-      <c r="V9" t="s">
-        <v>35</v>
-      </c>
-      <c r="X9">
+      <c r="P9" t="s">
+        <v>49</v>
+      </c>
+      <c r="W9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -696,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -708,19 +771,19 @@
         <v>-39</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J10">
         <v>59</v>
       </c>
       <c r="K10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -731,16 +794,19 @@
       <c r="O10">
         <v>8</v>
       </c>
-      <c r="R10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S10" t="s">
-        <v>44</v>
-      </c>
-      <c r="U10" t="s">
-        <v>35</v>
-      </c>
-      <c r="X10">
+      <c r="P10" t="s">
+        <v>50</v>
+      </c>
+      <c r="W10" t="s">
+        <v>51</v>
+      </c>
+      <c r="X10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -752,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -764,36 +830,39 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L11">
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>45</v>
-      </c>
-      <c r="R11" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" t="s">
-        <v>46</v>
-      </c>
-      <c r="U11" t="s">
-        <v>31</v>
-      </c>
-      <c r="X11">
+        <v>53</v>
+      </c>
+      <c r="P11" t="s">
+        <v>43</v>
+      </c>
+      <c r="W11" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -805,7 +874,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -817,36 +886,39 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I12" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L12">
         <v>8</v>
       </c>
       <c r="M12" t="s">
-        <v>45</v>
-      </c>
-      <c r="R12" t="s">
-        <v>31</v>
-      </c>
-      <c r="S12" t="s">
-        <v>47</v>
-      </c>
-      <c r="U12" t="s">
-        <v>31</v>
-      </c>
-      <c r="X12">
+        <v>53</v>
+      </c>
+      <c r="P12" t="s">
+        <v>30</v>
+      </c>
+      <c r="W12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X12" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -858,7 +930,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -870,36 +942,39 @@
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J13">
         <v>2</v>
       </c>
       <c r="K13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L13">
         <v>8</v>
       </c>
       <c r="M13" t="s">
-        <v>45</v>
-      </c>
-      <c r="R13" t="s">
-        <v>31</v>
-      </c>
-      <c r="S13" t="s">
-        <v>47</v>
-      </c>
-      <c r="U13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X13">
+        <v>53</v>
+      </c>
+      <c r="P13" t="s">
+        <v>49</v>
+      </c>
+      <c r="W13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X13" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -911,7 +986,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -923,36 +998,39 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
         <v>38</v>
-      </c>
-      <c r="I14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" t="s">
-        <v>34</v>
       </c>
       <c r="L14">
         <v>9</v>
       </c>
       <c r="M14" t="s">
-        <v>45</v>
-      </c>
-      <c r="R14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S14" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" t="s">
         <v>49</v>
       </c>
-      <c r="U14" t="s">
-        <v>35</v>
-      </c>
-      <c r="X14">
+      <c r="W14" t="s">
+        <v>35</v>
+      </c>
+      <c r="X14" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -964,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -973,15 +1051,15 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
-      </c>
-      <c r="X15">
+        <v>59</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -993,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1002,15 +1080,15 @@
         <v>-40</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I16" t="s">
-        <v>29</v>
-      </c>
-      <c r="X16">
+        <v>33</v>
+      </c>
+      <c r="AB16">
         <v>2</v>
       </c>
     </row>
@@ -1022,7 +1100,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1034,39 +1112,42 @@
         <v>-1</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17" t="s">
         <v>38</v>
-      </c>
-      <c r="I17" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17">
-        <v>3</v>
-      </c>
-      <c r="K17" t="s">
-        <v>34</v>
       </c>
       <c r="L17">
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>45</v>
-      </c>
-      <c r="R17" t="s">
-        <v>31</v>
-      </c>
-      <c r="S17" t="s">
-        <v>54</v>
-      </c>
-      <c r="T17" t="s">
-        <v>55</v>
-      </c>
-      <c r="U17" t="s">
-        <v>31</v>
-      </c>
-      <c r="X17">
+        <v>53</v>
+      </c>
+      <c r="P17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W17" t="s">
+        <v>35</v>
+      </c>
+      <c r="X17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -1078,7 +1159,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1090,39 +1171,42 @@
         <v>-4</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H18" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J18">
         <v>6</v>
       </c>
       <c r="K18" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L18">
         <v>7</v>
       </c>
       <c r="M18" t="s">
-        <v>56</v>
-      </c>
-      <c r="R18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S18" t="s">
-        <v>57</v>
-      </c>
-      <c r="T18" t="s">
-        <v>58</v>
-      </c>
-      <c r="U18" t="s">
-        <v>31</v>
-      </c>
-      <c r="X18">
+        <v>65</v>
+      </c>
+      <c r="P18" t="s">
+        <v>66</v>
+      </c>
+      <c r="W18" t="s">
+        <v>40</v>
+      </c>
+      <c r="X18" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -1134,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1146,39 +1230,42 @@
         <v>-10</v>
       </c>
       <c r="G19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J19">
         <v>7</v>
       </c>
       <c r="K19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
       <c r="M19" t="s">
-        <v>56</v>
-      </c>
-      <c r="R19" t="s">
-        <v>35</v>
-      </c>
-      <c r="S19" t="s">
-        <v>57</v>
-      </c>
-      <c r="T19" t="s">
-        <v>58</v>
-      </c>
-      <c r="U19" t="s">
-        <v>31</v>
-      </c>
-      <c r="X19">
+        <v>65</v>
+      </c>
+      <c r="P19" t="s">
+        <v>66</v>
+      </c>
+      <c r="W19" t="s">
+        <v>40</v>
+      </c>
+      <c r="X19" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -1190,7 +1277,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1202,39 +1289,42 @@
         <v>-17</v>
       </c>
       <c r="G20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I20" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L20">
         <v>7</v>
       </c>
       <c r="M20" t="s">
-        <v>41</v>
-      </c>
-      <c r="R20" t="s">
-        <v>35</v>
-      </c>
-      <c r="S20" t="s">
-        <v>59</v>
-      </c>
-      <c r="T20" t="s">
-        <v>60</v>
-      </c>
-      <c r="U20" t="s">
-        <v>35</v>
-      </c>
-      <c r="X20">
+        <v>47</v>
+      </c>
+      <c r="P20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB20">
         <v>1</v>
       </c>
     </row>
@@ -1246,7 +1336,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -1258,19 +1348,19 @@
         <v>-16</v>
       </c>
       <c r="G21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
       <c r="K21" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -1281,19 +1371,22 @@
       <c r="O21">
         <v>3</v>
       </c>
-      <c r="R21" t="s">
-        <v>35</v>
-      </c>
-      <c r="S21" t="s">
-        <v>61</v>
-      </c>
-      <c r="T21" t="s">
-        <v>62</v>
-      </c>
-      <c r="U21" t="s">
-        <v>35</v>
-      </c>
-      <c r="X21">
+      <c r="P21" t="s">
+        <v>66</v>
+      </c>
+      <c r="W21" t="s">
+        <v>40</v>
+      </c>
+      <c r="X21" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB21">
         <v>1</v>
       </c>
     </row>
@@ -1305,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1317,19 +1410,19 @@
         <v>-23</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J22">
         <v>12</v>
       </c>
       <c r="K22" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -1340,19 +1433,22 @@
       <c r="O22">
         <v>3</v>
       </c>
-      <c r="R22" t="s">
-        <v>31</v>
-      </c>
-      <c r="S22" t="s">
-        <v>44</v>
-      </c>
-      <c r="T22" t="s">
-        <v>63</v>
-      </c>
-      <c r="U22" t="s">
-        <v>35</v>
-      </c>
-      <c r="X22">
+      <c r="P22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22" t="s">
+        <v>35</v>
+      </c>
+      <c r="X22" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB22">
         <v>1</v>
       </c>
     </row>
@@ -1364,7 +1460,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1376,39 +1472,42 @@
         <v>-35</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H23" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I23" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J23">
         <v>4</v>
       </c>
       <c r="K23" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L23">
         <v>6</v>
       </c>
       <c r="M23" t="s">
-        <v>64</v>
-      </c>
-      <c r="R23" t="s">
-        <v>31</v>
-      </c>
-      <c r="S23" t="s">
-        <v>65</v>
-      </c>
-      <c r="T23" t="s">
-        <v>66</v>
-      </c>
-      <c r="U23" t="s">
-        <v>35</v>
-      </c>
-      <c r="X23">
+        <v>74</v>
+      </c>
+      <c r="P23" t="s">
+        <v>43</v>
+      </c>
+      <c r="W23" t="s">
+        <v>35</v>
+      </c>
+      <c r="X23" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB23">
         <v>1</v>
       </c>
     </row>
@@ -1420,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1432,19 +1531,19 @@
         <v>-39</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -1455,19 +1554,22 @@
       <c r="O24">
         <v>1</v>
       </c>
-      <c r="R24" t="s">
-        <v>31</v>
-      </c>
-      <c r="S24" t="s">
-        <v>49</v>
-      </c>
-      <c r="T24" t="s">
-        <v>62</v>
-      </c>
-      <c r="U24" t="s">
-        <v>31</v>
-      </c>
-      <c r="X24">
+      <c r="P24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W24" t="s">
+        <v>35</v>
+      </c>
+      <c r="X24" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB24">
         <v>1</v>
       </c>
     </row>
@@ -1479,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1491,19 +1593,19 @@
         <v>-40</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -1514,19 +1616,22 @@
       <c r="O25">
         <v>2</v>
       </c>
-      <c r="R25" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" t="s">
-        <v>44</v>
-      </c>
-      <c r="T25" t="s">
-        <v>67</v>
-      </c>
-      <c r="U25" t="s">
-        <v>35</v>
-      </c>
-      <c r="X25">
+      <c r="P25" t="s">
+        <v>49</v>
+      </c>
+      <c r="W25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X25" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB25">
         <v>1</v>
       </c>
     </row>
@@ -1538,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1550,39 +1655,42 @@
         <v>-46</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I26" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J26">
         <v>5</v>
       </c>
       <c r="K26" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L26">
         <v>7</v>
       </c>
       <c r="M26" t="s">
-        <v>56</v>
-      </c>
-      <c r="R26" t="s">
-        <v>31</v>
-      </c>
-      <c r="S26" t="s">
-        <v>68</v>
-      </c>
-      <c r="T26" t="s">
-        <v>69</v>
-      </c>
-      <c r="U26" t="s">
-        <v>35</v>
-      </c>
-      <c r="X26">
+        <v>65</v>
+      </c>
+      <c r="P26" t="s">
+        <v>43</v>
+      </c>
+      <c r="W26" t="s">
+        <v>35</v>
+      </c>
+      <c r="X26" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB26">
         <v>1</v>
       </c>
     </row>
@@ -1594,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1606,39 +1714,42 @@
         <v>49</v>
       </c>
       <c r="G27" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H27" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I27" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J27">
         <v>-3</v>
       </c>
       <c r="K27" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L27">
         <v>6</v>
       </c>
       <c r="M27" t="s">
-        <v>41</v>
-      </c>
-      <c r="R27" t="s">
-        <v>31</v>
-      </c>
-      <c r="S27" t="s">
-        <v>70</v>
-      </c>
-      <c r="T27" t="s">
-        <v>71</v>
-      </c>
-      <c r="U27" t="s">
-        <v>35</v>
-      </c>
-      <c r="X27">
+        <v>47</v>
+      </c>
+      <c r="P27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" t="s">
+        <v>35</v>
+      </c>
+      <c r="X27" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB27">
         <v>1</v>
       </c>
     </row>
@@ -1650,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -1662,39 +1773,42 @@
         <v>-48</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J28">
         <v>-9</v>
       </c>
       <c r="K28" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L28">
         <v>4</v>
       </c>
       <c r="M28" t="s">
+        <v>47</v>
+      </c>
+      <c r="P28" t="s">
+        <v>30</v>
+      </c>
+      <c r="W28" t="s">
+        <v>35</v>
+      </c>
+      <c r="X28" t="s">
         <v>41</v>
       </c>
-      <c r="R28" t="s">
-        <v>31</v>
-      </c>
-      <c r="S28" t="s">
-        <v>36</v>
-      </c>
-      <c r="T28" t="s">
-        <v>72</v>
-      </c>
-      <c r="U28" t="s">
-        <v>31</v>
-      </c>
-      <c r="X28">
+      <c r="Y28" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB28">
         <v>1</v>
       </c>
     </row>
@@ -1706,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1718,16 +1832,16 @@
         <v>-39</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I29" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -1738,19 +1852,22 @@
       <c r="O29">
         <v>1</v>
       </c>
-      <c r="R29" t="s">
-        <v>35</v>
-      </c>
-      <c r="S29" t="s">
-        <v>36</v>
-      </c>
-      <c r="T29" t="s">
-        <v>74</v>
-      </c>
-      <c r="U29" t="s">
-        <v>31</v>
-      </c>
-      <c r="X29">
+      <c r="P29" t="s">
+        <v>43</v>
+      </c>
+      <c r="W29" t="s">
+        <v>40</v>
+      </c>
+      <c r="X29" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB29">
         <v>1</v>
       </c>
     </row>
@@ -1762,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1774,36 +1891,39 @@
         <v>3</v>
       </c>
       <c r="G30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I30" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J30">
         <v>-4</v>
       </c>
       <c r="K30" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L30">
         <v>9</v>
       </c>
       <c r="M30" t="s">
-        <v>56</v>
-      </c>
-      <c r="R30" t="s">
-        <v>35</v>
-      </c>
-      <c r="S30" t="s">
-        <v>75</v>
-      </c>
-      <c r="U30" t="s">
-        <v>35</v>
-      </c>
-      <c r="X30">
+        <v>65</v>
+      </c>
+      <c r="P30" t="s">
+        <v>30</v>
+      </c>
+      <c r="W30" t="s">
+        <v>40</v>
+      </c>
+      <c r="X30" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1815,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1827,19 +1947,19 @@
         <v>7</v>
       </c>
       <c r="G31" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I31" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J31">
         <v>7</v>
       </c>
       <c r="K31" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -1850,16 +1970,19 @@
       <c r="O31">
         <v>6</v>
       </c>
-      <c r="R31" t="s">
-        <v>35</v>
-      </c>
-      <c r="S31" t="s">
-        <v>77</v>
-      </c>
-      <c r="U31" t="s">
-        <v>35</v>
-      </c>
-      <c r="X31">
+      <c r="P31" t="s">
+        <v>43</v>
+      </c>
+      <c r="W31" t="s">
+        <v>40</v>
+      </c>
+      <c r="X31" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
     </row>
@@ -1871,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1880,15 +2003,15 @@
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
-      </c>
-      <c r="X32">
+        <v>59</v>
+      </c>
+      <c r="AB32">
         <v>2</v>
       </c>
     </row>
@@ -1900,19 +2023,19 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F33">
         <v>-40</v>
       </c>
       <c r="G33" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I33" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
@@ -1923,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1935,39 +2058,42 @@
         <v>-32</v>
       </c>
       <c r="G34" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H34" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34" t="s">
         <v>38</v>
-      </c>
-      <c r="I34" t="s">
-        <v>39</v>
-      </c>
-      <c r="J34">
-        <v>2</v>
-      </c>
-      <c r="K34" t="s">
-        <v>34</v>
       </c>
       <c r="L34">
         <v>7</v>
       </c>
       <c r="M34" t="s">
-        <v>45</v>
-      </c>
-      <c r="R34" t="s">
-        <v>35</v>
-      </c>
-      <c r="S34" t="s">
-        <v>59</v>
-      </c>
-      <c r="T34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U34" t="s">
-        <v>31</v>
-      </c>
-      <c r="X34">
+        <v>53</v>
+      </c>
+      <c r="P34" t="s">
+        <v>49</v>
+      </c>
+      <c r="W34" t="s">
+        <v>40</v>
+      </c>
+      <c r="X34" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB34">
         <v>2</v>
       </c>
     </row>
@@ -1979,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -1991,39 +2117,42 @@
         <v>-34</v>
       </c>
       <c r="G35" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H35" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I35" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J35">
         <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L35">
         <v>6</v>
       </c>
       <c r="M35" t="s">
-        <v>45</v>
-      </c>
-      <c r="R35" t="s">
-        <v>31</v>
-      </c>
-      <c r="S35" t="s">
-        <v>70</v>
-      </c>
-      <c r="T35" t="s">
-        <v>71</v>
-      </c>
-      <c r="U35" t="s">
-        <v>31</v>
-      </c>
-      <c r="X35">
+        <v>53</v>
+      </c>
+      <c r="P35" t="s">
+        <v>30</v>
+      </c>
+      <c r="W35" t="s">
+        <v>35</v>
+      </c>
+      <c r="X35" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB35">
         <v>2</v>
       </c>
     </row>
@@ -2035,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2047,39 +2176,42 @@
         <v>-47</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H36" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I36" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J36">
         <v>30</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L36">
         <v>6</v>
       </c>
       <c r="M36" t="s">
-        <v>41</v>
-      </c>
-      <c r="R36" t="s">
-        <v>31</v>
-      </c>
-      <c r="S36" t="s">
-        <v>65</v>
-      </c>
-      <c r="T36" t="s">
-        <v>66</v>
-      </c>
-      <c r="U36" t="s">
-        <v>31</v>
-      </c>
-      <c r="X36">
+        <v>47</v>
+      </c>
+      <c r="P36" t="s">
+        <v>43</v>
+      </c>
+      <c r="W36" t="s">
+        <v>35</v>
+      </c>
+      <c r="X36" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB36">
         <v>2</v>
       </c>
     </row>
@@ -2091,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2103,39 +2235,42 @@
         <v>23</v>
       </c>
       <c r="G37" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H37" t="s">
+        <v>44</v>
+      </c>
+      <c r="I37" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37">
+        <v>3</v>
+      </c>
+      <c r="K37" t="s">
         <v>38</v>
-      </c>
-      <c r="I37" t="s">
-        <v>39</v>
-      </c>
-      <c r="J37">
-        <v>3</v>
-      </c>
-      <c r="K37" t="s">
-        <v>34</v>
       </c>
       <c r="L37">
         <v>6</v>
       </c>
       <c r="M37" t="s">
-        <v>56</v>
-      </c>
-      <c r="R37" t="s">
-        <v>35</v>
-      </c>
-      <c r="S37" t="s">
-        <v>57</v>
-      </c>
-      <c r="T37" t="s">
-        <v>79</v>
-      </c>
-      <c r="U37" t="s">
-        <v>35</v>
-      </c>
-      <c r="X37">
+        <v>65</v>
+      </c>
+      <c r="P37" t="s">
+        <v>89</v>
+      </c>
+      <c r="W37" t="s">
+        <v>40</v>
+      </c>
+      <c r="X37" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB37">
         <v>2</v>
       </c>
     </row>
@@ -2147,7 +2282,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
@@ -2158,7 +2293,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2170,39 +2305,42 @@
         <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H39" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I39" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J39">
         <v>5</v>
       </c>
       <c r="K39" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L39">
         <v>7</v>
       </c>
       <c r="M39" t="s">
-        <v>41</v>
-      </c>
-      <c r="R39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S39" t="s">
-        <v>57</v>
-      </c>
-      <c r="T39" t="s">
-        <v>58</v>
-      </c>
-      <c r="U39" t="s">
-        <v>31</v>
-      </c>
-      <c r="X39">
+        <v>47</v>
+      </c>
+      <c r="P39" t="s">
+        <v>89</v>
+      </c>
+      <c r="W39" t="s">
+        <v>40</v>
+      </c>
+      <c r="X39" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB39">
         <v>2</v>
       </c>
     </row>
@@ -2214,7 +2352,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2226,39 +2364,42 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I40" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J40">
         <v>2</v>
       </c>
       <c r="K40" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L40">
         <v>7</v>
       </c>
       <c r="M40" t="s">
-        <v>56</v>
-      </c>
-      <c r="R40" t="s">
-        <v>35</v>
-      </c>
-      <c r="S40" t="s">
-        <v>61</v>
-      </c>
-      <c r="T40" t="s">
-        <v>80</v>
-      </c>
-      <c r="U40" t="s">
-        <v>31</v>
-      </c>
-      <c r="X40">
+        <v>65</v>
+      </c>
+      <c r="P40" t="s">
+        <v>66</v>
+      </c>
+      <c r="W40" t="s">
+        <v>40</v>
+      </c>
+      <c r="X40" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB40">
         <v>2</v>
       </c>
     </row>
@@ -2270,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2282,42 +2423,45 @@
         <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H41" t="s">
+        <v>44</v>
+      </c>
+      <c r="I41" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
         <v>38</v>
-      </c>
-      <c r="I41" t="s">
-        <v>39</v>
-      </c>
-      <c r="J41">
-        <v>2</v>
-      </c>
-      <c r="K41" t="s">
-        <v>34</v>
       </c>
       <c r="L41">
         <v>6</v>
       </c>
       <c r="M41" t="s">
-        <v>45</v>
-      </c>
-      <c r="R41" t="s">
-        <v>35</v>
-      </c>
-      <c r="S41" t="s">
-        <v>65</v>
-      </c>
-      <c r="T41" t="s">
-        <v>60</v>
-      </c>
-      <c r="U41" t="s">
-        <v>35</v>
-      </c>
-      <c r="V41" t="s">
-        <v>35</v>
-      </c>
-      <c r="X41">
+        <v>53</v>
+      </c>
+      <c r="P41" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" t="s">
+        <v>40</v>
+      </c>
+      <c r="X41" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB41">
         <v>2</v>
       </c>
     </row>
@@ -2329,7 +2473,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2341,36 +2485,39 @@
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I42" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J42">
         <v>-4</v>
       </c>
       <c r="K42" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L42">
         <v>7</v>
       </c>
-      <c r="R42" t="s">
-        <v>35</v>
-      </c>
-      <c r="S42" t="s">
-        <v>70</v>
-      </c>
-      <c r="T42" t="s">
-        <v>82</v>
-      </c>
-      <c r="U42" t="s">
-        <v>31</v>
-      </c>
-      <c r="X42">
+      <c r="P42" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" t="s">
+        <v>40</v>
+      </c>
+      <c r="X42" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB42">
         <v>2</v>
       </c>
     </row>
@@ -2382,7 +2529,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -2394,19 +2541,19 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -2417,19 +2564,22 @@
       <c r="O43">
         <v>1</v>
       </c>
-      <c r="R43" t="s">
-        <v>35</v>
-      </c>
-      <c r="S43" t="s">
-        <v>44</v>
-      </c>
-      <c r="T43" t="s">
-        <v>83</v>
-      </c>
-      <c r="U43" t="s">
-        <v>31</v>
-      </c>
-      <c r="X43">
+      <c r="P43" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" t="s">
+        <v>40</v>
+      </c>
+      <c r="X43" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB43">
         <v>2</v>
       </c>
     </row>
@@ -2441,7 +2591,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45">
@@ -2452,7 +2602,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2464,19 +2614,19 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I45" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L45">
         <v>6</v>
@@ -2487,19 +2637,22 @@
       <c r="O45">
         <v>4</v>
       </c>
-      <c r="R45" t="s">
-        <v>35</v>
-      </c>
-      <c r="S45" t="s">
-        <v>70</v>
-      </c>
-      <c r="T45" t="s">
-        <v>82</v>
-      </c>
-      <c r="U45" t="s">
-        <v>31</v>
-      </c>
-      <c r="X45">
+      <c r="P45" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" t="s">
+        <v>40</v>
+      </c>
+      <c r="X45" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB45">
         <v>2</v>
       </c>
     </row>
@@ -2511,7 +2664,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2523,36 +2676,39 @@
         <v>-15</v>
       </c>
       <c r="G46" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H46" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I46" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L46">
         <v>7</v>
       </c>
       <c r="M46" t="s">
-        <v>64</v>
-      </c>
-      <c r="R46" t="s">
-        <v>31</v>
-      </c>
-      <c r="S46" t="s">
-        <v>61</v>
-      </c>
-      <c r="U46" t="s">
-        <v>31</v>
-      </c>
-      <c r="X46">
+        <v>74</v>
+      </c>
+      <c r="P46" t="s">
+        <v>95</v>
+      </c>
+      <c r="W46" t="s">
+        <v>35</v>
+      </c>
+      <c r="X46" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB46">
         <v>3</v>
       </c>
     </row>
@@ -2564,7 +2720,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2576,18 +2732,18 @@
         <v>-16</v>
       </c>
       <c r="G47" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I47" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J47">
         <v>-5</v>
       </c>
       <c r="K47" t="s">
-        <v>40</v>
-      </c>
-      <c r="X47">
+        <v>46</v>
+      </c>
+      <c r="AB47">
         <v>3</v>
       </c>
     </row>
@@ -2599,7 +2755,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2611,19 +2767,19 @@
         <v>-11</v>
       </c>
       <c r="G48" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I48" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J48">
         <v>26</v>
       </c>
       <c r="K48" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L48">
         <v>6</v>
@@ -2634,13 +2790,16 @@
       <c r="O48">
         <v>5</v>
       </c>
-      <c r="R48" t="s">
-        <v>35</v>
-      </c>
-      <c r="U48" t="s">
-        <v>31</v>
-      </c>
-      <c r="X48">
+      <c r="P48" t="s">
+        <v>30</v>
+      </c>
+      <c r="W48" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB48">
         <v>3</v>
       </c>
     </row>
@@ -2652,7 +2811,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2664,19 +2823,19 @@
         <v>-37</v>
       </c>
       <c r="G49" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J49">
         <v>29</v>
       </c>
       <c r="K49" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L49">
         <v>6</v>
@@ -2687,16 +2846,19 @@
       <c r="O49">
         <v>7</v>
       </c>
-      <c r="R49" t="s">
-        <v>35</v>
-      </c>
-      <c r="S49" t="s">
-        <v>84</v>
-      </c>
-      <c r="U49" t="s">
-        <v>31</v>
-      </c>
-      <c r="X49">
+      <c r="P49" t="s">
+        <v>43</v>
+      </c>
+      <c r="W49" t="s">
+        <v>40</v>
+      </c>
+      <c r="X49" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB49">
         <v>3</v>
       </c>
     </row>
@@ -2708,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2720,21 +2882,24 @@
         <v>34</v>
       </c>
       <c r="G50" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I50" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J50">
         <v>5</v>
       </c>
       <c r="K50" t="s">
-        <v>34</v>
-      </c>
-      <c r="R50" t="s">
-        <v>35</v>
-      </c>
-      <c r="X50">
+        <v>38</v>
+      </c>
+      <c r="P50" t="s">
+        <v>43</v>
+      </c>
+      <c r="W50" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB50">
         <v>3</v>
       </c>
     </row>
@@ -2746,7 +2911,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2758,19 +2923,19 @@
         <v>29</v>
       </c>
       <c r="G51" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I51" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J51">
         <v>2</v>
       </c>
       <c r="K51" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L51">
         <v>6</v>
@@ -2781,13 +2946,16 @@
       <c r="O51">
         <v>1</v>
       </c>
-      <c r="R51" t="s">
-        <v>43</v>
-      </c>
-      <c r="U51" t="s">
-        <v>31</v>
-      </c>
-      <c r="X51">
+      <c r="P51" t="s">
+        <v>50</v>
+      </c>
+      <c r="W51" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB51">
         <v>3</v>
       </c>
     </row>
@@ -2799,7 +2967,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -2811,19 +2979,19 @@
         <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I52" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J52">
         <v>19</v>
       </c>
       <c r="K52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L52">
         <v>7</v>
@@ -2834,13 +3002,16 @@
       <c r="O52">
         <v>3</v>
       </c>
-      <c r="R52" t="s">
-        <v>35</v>
-      </c>
-      <c r="U52" t="s">
-        <v>35</v>
-      </c>
-      <c r="X52">
+      <c r="P52" t="s">
+        <v>49</v>
+      </c>
+      <c r="W52" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB52">
         <v>3</v>
       </c>
     </row>
@@ -2852,7 +3023,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2864,19 +3035,19 @@
         <v>8</v>
       </c>
       <c r="G53" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H53" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I53" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L53">
         <v>6</v>
@@ -2887,16 +3058,19 @@
       <c r="O53">
         <v>3</v>
       </c>
-      <c r="R53" t="s">
-        <v>31</v>
-      </c>
-      <c r="S53" t="s">
-        <v>85</v>
-      </c>
-      <c r="U53" t="s">
-        <v>35</v>
-      </c>
-      <c r="X53">
+      <c r="P53" t="s">
+        <v>49</v>
+      </c>
+      <c r="W53" t="s">
+        <v>35</v>
+      </c>
+      <c r="X53" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB53">
         <v>3</v>
       </c>
     </row>
@@ -2908,7 +3082,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -2920,33 +3094,36 @@
         <v>8</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H54" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I54" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J54">
         <v>-1</v>
       </c>
       <c r="K54" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L54">
         <v>6</v>
       </c>
-      <c r="R54" t="s">
-        <v>43</v>
-      </c>
-      <c r="S54" t="s">
-        <v>44</v>
-      </c>
-      <c r="U54" t="s">
-        <v>31</v>
-      </c>
-      <c r="X54">
+      <c r="P54" t="s">
+        <v>50</v>
+      </c>
+      <c r="W54" t="s">
+        <v>51</v>
+      </c>
+      <c r="X54" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB54">
         <v>3</v>
       </c>
     </row>
@@ -2958,7 +3135,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D55">
         <v>3</v>
@@ -2970,36 +3147,39 @@
         <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H55" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I55" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J55">
         <v>9</v>
       </c>
       <c r="K55" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L55">
         <v>7</v>
       </c>
       <c r="M55" t="s">
-        <v>56</v>
-      </c>
-      <c r="R55" t="s">
-        <v>35</v>
-      </c>
-      <c r="S55" t="s">
-        <v>70</v>
-      </c>
-      <c r="U55" t="s">
-        <v>35</v>
-      </c>
-      <c r="X55">
+        <v>65</v>
+      </c>
+      <c r="P55" t="s">
+        <v>43</v>
+      </c>
+      <c r="W55" t="s">
+        <v>40</v>
+      </c>
+      <c r="X55" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB55">
         <v>3</v>
       </c>
     </row>
@@ -3011,7 +3191,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3020,15 +3200,15 @@
         <v>3</v>
       </c>
       <c r="G56" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I56" t="s">
-        <v>51</v>
-      </c>
-      <c r="X56">
+        <v>59</v>
+      </c>
+      <c r="AB56">
         <v>3</v>
       </c>
     </row>
@@ -3040,7 +3220,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -3049,15 +3229,15 @@
         <v>-40</v>
       </c>
       <c r="G57" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I57" t="s">
-        <v>29</v>
-      </c>
-      <c r="X57">
+        <v>33</v>
+      </c>
+      <c r="AB57">
         <v>4</v>
       </c>
     </row>
@@ -3069,7 +3249,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59">
@@ -3080,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3092,39 +3272,42 @@
         <v>-8</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H59" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I59" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L59">
         <v>7</v>
       </c>
       <c r="M59" t="s">
-        <v>41</v>
-      </c>
-      <c r="R59" t="s">
-        <v>31</v>
-      </c>
-      <c r="S59" t="s">
-        <v>65</v>
-      </c>
-      <c r="T59" t="s">
-        <v>66</v>
-      </c>
-      <c r="U59" t="s">
-        <v>31</v>
-      </c>
-      <c r="X59">
+        <v>47</v>
+      </c>
+      <c r="P59" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" t="s">
+        <v>35</v>
+      </c>
+      <c r="X59" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB59">
         <v>3</v>
       </c>
     </row>
@@ -3136,7 +3319,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3148,19 +3331,19 @@
         <v>-8</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H60" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I60" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J60">
         <v>6</v>
       </c>
       <c r="K60" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L60">
         <v>7</v>
@@ -3171,19 +3354,22 @@
       <c r="O60">
         <v>3</v>
       </c>
-      <c r="R60" t="s">
-        <v>35</v>
-      </c>
-      <c r="S60" t="s">
-        <v>61</v>
-      </c>
-      <c r="T60" t="s">
-        <v>62</v>
-      </c>
-      <c r="U60" t="s">
-        <v>35</v>
-      </c>
-      <c r="X60">
+      <c r="P60" t="s">
+        <v>66</v>
+      </c>
+      <c r="W60" t="s">
+        <v>40</v>
+      </c>
+      <c r="X60" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB60">
         <v>3</v>
       </c>
     </row>
@@ -3195,7 +3381,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -3207,19 +3393,19 @@
         <v>-14</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H61" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I61" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -3230,19 +3416,22 @@
       <c r="O61">
         <v>2</v>
       </c>
-      <c r="R61" t="s">
-        <v>31</v>
-      </c>
-      <c r="S61" t="s">
-        <v>44</v>
-      </c>
-      <c r="T61" t="s">
-        <v>67</v>
-      </c>
-      <c r="U61" t="s">
-        <v>31</v>
-      </c>
-      <c r="X61">
+      <c r="P61" t="s">
+        <v>49</v>
+      </c>
+      <c r="W61" t="s">
+        <v>35</v>
+      </c>
+      <c r="X61" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB61">
         <v>3</v>
       </c>
     </row>
@@ -3254,7 +3443,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -3266,15 +3455,15 @@
         <v>-14</v>
       </c>
       <c r="G62" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H62" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I62" t="s">
-        <v>87</v>
-      </c>
-      <c r="X62">
+        <v>99</v>
+      </c>
+      <c r="AB62">
         <v>3</v>
       </c>
     </row>
@@ -3286,7 +3475,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3298,36 +3487,39 @@
         <v>47</v>
       </c>
       <c r="G63" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I63" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J63">
         <v>10</v>
       </c>
       <c r="K63" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L63">
         <v>6</v>
       </c>
-      <c r="Q63">
+      <c r="P63" t="s">
+        <v>49</v>
+      </c>
+      <c r="V63">
         <v>0</v>
       </c>
-      <c r="R63" t="s">
-        <v>35</v>
-      </c>
-      <c r="S63" t="s">
-        <v>85</v>
-      </c>
-      <c r="U63" t="s">
-        <v>31</v>
-      </c>
-      <c r="X63">
+      <c r="W63" t="s">
+        <v>40</v>
+      </c>
+      <c r="X63" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB63">
         <v>4</v>
       </c>
     </row>
@@ -3339,7 +3531,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3351,19 +3543,19 @@
         <v>37</v>
       </c>
       <c r="G64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I64" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J64">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L64">
         <v>7</v>
@@ -3374,16 +3566,19 @@
       <c r="O64">
         <v>2</v>
       </c>
-      <c r="R64" t="s">
-        <v>35</v>
-      </c>
-      <c r="S64" t="s">
-        <v>85</v>
-      </c>
-      <c r="U64" t="s">
-        <v>35</v>
-      </c>
-      <c r="X64">
+      <c r="P64" t="s">
+        <v>49</v>
+      </c>
+      <c r="W64" t="s">
+        <v>40</v>
+      </c>
+      <c r="X64" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB64">
         <v>4</v>
       </c>
     </row>
@@ -3395,7 +3590,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3407,19 +3602,19 @@
         <v>36</v>
       </c>
       <c r="G65" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H65" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I65" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J65">
         <v>36</v>
       </c>
       <c r="K65" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L65">
         <v>6</v>
@@ -3430,13 +3625,16 @@
       <c r="O65">
         <v>8</v>
       </c>
-      <c r="R65" t="s">
-        <v>31</v>
-      </c>
-      <c r="U65" t="s">
-        <v>35</v>
-      </c>
-      <c r="X65">
+      <c r="P65" t="s">
+        <v>49</v>
+      </c>
+      <c r="W65" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB65">
         <v>4</v>
       </c>
     </row>
@@ -3448,7 +3646,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3457,15 +3655,15 @@
         <v>3</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H66" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I66" t="s">
-        <v>51</v>
-      </c>
-      <c r="X66">
+        <v>59</v>
+      </c>
+      <c r="AB66">
         <v>4</v>
       </c>
     </row>
@@ -3477,7 +3675,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3486,15 +3684,15 @@
         <v>-40</v>
       </c>
       <c r="G67" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H67" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I67" t="s">
-        <v>29</v>
-      </c>
-      <c r="X67">
+        <v>33</v>
+      </c>
+      <c r="AB67">
         <v>5</v>
       </c>
     </row>
@@ -3506,7 +3704,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
@@ -3517,7 +3715,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3529,39 +3727,42 @@
         <v>-22</v>
       </c>
       <c r="G69" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H69" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I69" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J69">
         <v>6</v>
       </c>
       <c r="K69" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L69">
         <v>7</v>
       </c>
       <c r="M69" t="s">
-        <v>45</v>
-      </c>
-      <c r="R69" t="s">
-        <v>35</v>
-      </c>
-      <c r="S69" t="s">
-        <v>57</v>
-      </c>
-      <c r="T69" t="s">
-        <v>80</v>
-      </c>
-      <c r="U69" t="s">
-        <v>31</v>
-      </c>
-      <c r="X69">
+        <v>53</v>
+      </c>
+      <c r="P69" t="s">
+        <v>101</v>
+      </c>
+      <c r="W69" t="s">
+        <v>40</v>
+      </c>
+      <c r="X69" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB69">
         <v>4</v>
       </c>
     </row>
@@ -3573,7 +3774,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -3585,39 +3786,42 @@
         <v>-28</v>
       </c>
       <c r="G70" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I70" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J70">
         <v>-10</v>
       </c>
       <c r="K70" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L70">
         <v>7</v>
       </c>
       <c r="M70" t="s">
-        <v>56</v>
-      </c>
-      <c r="R70" t="s">
-        <v>35</v>
-      </c>
-      <c r="S70" t="s">
-        <v>59</v>
-      </c>
-      <c r="T70" t="s">
-        <v>78</v>
-      </c>
-      <c r="U70" t="s">
-        <v>35</v>
-      </c>
-      <c r="X70">
+        <v>65</v>
+      </c>
+      <c r="P70" t="s">
+        <v>30</v>
+      </c>
+      <c r="W70" t="s">
+        <v>40</v>
+      </c>
+      <c r="X70" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB70">
         <v>4</v>
       </c>
     </row>
@@ -3629,7 +3833,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -3641,39 +3845,42 @@
         <v>-18</v>
       </c>
       <c r="G71" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H71" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I71" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J71">
         <v>6</v>
       </c>
       <c r="K71" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L71">
         <v>6</v>
       </c>
       <c r="M71" t="s">
-        <v>41</v>
-      </c>
-      <c r="R71" t="s">
-        <v>35</v>
-      </c>
-      <c r="S71" t="s">
-        <v>70</v>
-      </c>
-      <c r="T71" t="s">
-        <v>89</v>
-      </c>
-      <c r="U71" t="s">
-        <v>35</v>
-      </c>
-      <c r="X71">
+        <v>47</v>
+      </c>
+      <c r="P71" t="s">
+        <v>30</v>
+      </c>
+      <c r="W71" t="s">
+        <v>40</v>
+      </c>
+      <c r="X71" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB71">
         <v>4</v>
       </c>
     </row>
@@ -3685,7 +3892,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -3697,39 +3904,42 @@
         <v>-24</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H72" t="s">
+        <v>44</v>
+      </c>
+      <c r="I72" t="s">
+        <v>45</v>
+      </c>
+      <c r="J72">
+        <v>2</v>
+      </c>
+      <c r="K72" t="s">
         <v>38</v>
-      </c>
-      <c r="I72" t="s">
-        <v>39</v>
-      </c>
-      <c r="J72">
-        <v>2</v>
-      </c>
-      <c r="K72" t="s">
-        <v>34</v>
       </c>
       <c r="L72">
         <v>6</v>
       </c>
       <c r="M72" t="s">
-        <v>56</v>
-      </c>
-      <c r="R72" t="s">
-        <v>31</v>
-      </c>
-      <c r="S72" t="s">
-        <v>59</v>
-      </c>
-      <c r="T72" t="s">
-        <v>90</v>
-      </c>
-      <c r="U72" t="s">
-        <v>31</v>
-      </c>
-      <c r="X72">
+        <v>65</v>
+      </c>
+      <c r="P72" t="s">
+        <v>49</v>
+      </c>
+      <c r="W72" t="s">
+        <v>35</v>
+      </c>
+      <c r="X72" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB72">
         <v>4</v>
       </c>
     </row>
@@ -3741,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -3753,15 +3963,15 @@
         <v>-26</v>
       </c>
       <c r="G73" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H73" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I73" t="s">
-        <v>91</v>
-      </c>
-      <c r="X73">
+        <v>104</v>
+      </c>
+      <c r="AB73">
         <v>4</v>
       </c>
     </row>
@@ -3773,7 +3983,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3785,39 +3995,42 @@
         <v>47</v>
       </c>
       <c r="G74" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H74" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I74" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J74">
         <v>47</v>
       </c>
       <c r="K74" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L74">
         <v>8</v>
       </c>
       <c r="M74" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q74">
+        <v>65</v>
+      </c>
+      <c r="P74" t="s">
+        <v>95</v>
+      </c>
+      <c r="V74">
         <v>0</v>
       </c>
-      <c r="R74" t="s">
-        <v>35</v>
-      </c>
-      <c r="S74" t="s">
-        <v>61</v>
-      </c>
-      <c r="U74" t="s">
-        <v>31</v>
-      </c>
-      <c r="X74">
+      <c r="W74" t="s">
+        <v>40</v>
+      </c>
+      <c r="X74" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB74">
         <v>5</v>
       </c>
     </row>
@@ -3829,7 +4042,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3838,15 +4051,15 @@
         <v>3</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H75" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I75" t="s">
-        <v>92</v>
-      </c>
-      <c r="X75">
+        <v>105</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -3858,7 +4071,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3867,15 +4080,15 @@
         <v>-40</v>
       </c>
       <c r="G76" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H76" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I76" t="s">
-        <v>29</v>
-      </c>
-      <c r="X76">
+        <v>33</v>
+      </c>
+      <c r="AB76">
         <v>6</v>
       </c>
     </row>
@@ -3887,7 +4100,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3899,19 +4112,19 @@
         <v>-22</v>
       </c>
       <c r="G77" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H77" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I77" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J77">
         <v>7</v>
       </c>
       <c r="K77" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L77">
         <v>6</v>
@@ -3922,19 +4135,22 @@
       <c r="O77">
         <v>1</v>
       </c>
-      <c r="R77" t="s">
-        <v>35</v>
-      </c>
-      <c r="S77" t="s">
-        <v>36</v>
-      </c>
-      <c r="T77" t="s">
-        <v>93</v>
-      </c>
-      <c r="U77" t="s">
-        <v>31</v>
-      </c>
-      <c r="X77">
+      <c r="P77" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" t="s">
+        <v>40</v>
+      </c>
+      <c r="X77" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB77">
         <v>5</v>
       </c>
     </row>
@@ -3946,7 +4162,7 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3958,24 +4174,27 @@
         <v>-29</v>
       </c>
       <c r="G78" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I78" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J78">
         <v>-5</v>
       </c>
       <c r="K78" t="s">
-        <v>34</v>
-      </c>
-      <c r="R78" t="s">
-        <v>35</v>
-      </c>
-      <c r="S78" t="s">
-        <v>36</v>
-      </c>
-      <c r="X78">
+        <v>38</v>
+      </c>
+      <c r="P78" t="s">
+        <v>49</v>
+      </c>
+      <c r="W78" t="s">
+        <v>40</v>
+      </c>
+      <c r="X78" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB78">
         <v>5</v>
       </c>
     </row>
@@ -3987,7 +4206,7 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -3999,36 +4218,39 @@
         <v>-24</v>
       </c>
       <c r="G79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H79" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I79" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J79">
         <v>6</v>
       </c>
       <c r="K79" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L79">
         <v>5</v>
       </c>
-      <c r="R79" t="s">
-        <v>35</v>
-      </c>
-      <c r="S79" t="s">
-        <v>36</v>
-      </c>
-      <c r="T79" t="s">
-        <v>63</v>
-      </c>
-      <c r="U79" t="s">
-        <v>31</v>
-      </c>
-      <c r="X79">
+      <c r="P79" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" t="s">
+        <v>40</v>
+      </c>
+      <c r="X79" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB79">
         <v>5</v>
       </c>
     </row>
@@ -4040,7 +4262,7 @@
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -4052,39 +4274,42 @@
         <v>-30</v>
       </c>
       <c r="G80" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H80" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I80" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J80">
         <v>13</v>
       </c>
       <c r="K80" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L80">
         <v>5</v>
       </c>
       <c r="M80" t="s">
-        <v>56</v>
-      </c>
-      <c r="R80" t="s">
-        <v>35</v>
-      </c>
-      <c r="S80" t="s">
-        <v>36</v>
-      </c>
-      <c r="T80" t="s">
-        <v>72</v>
-      </c>
-      <c r="U80" t="s">
-        <v>31</v>
-      </c>
-      <c r="X80">
+        <v>65</v>
+      </c>
+      <c r="P80" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" t="s">
+        <v>40</v>
+      </c>
+      <c r="X80" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB80">
         <v>5</v>
       </c>
     </row>
@@ -4096,7 +4321,7 @@
         <v>2</v>
       </c>
       <c r="C81" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -4108,36 +4333,39 @@
         <v>-43</v>
       </c>
       <c r="G81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H81" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I81" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J81">
         <v>-8</v>
       </c>
       <c r="K81" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L81">
         <v>5</v>
       </c>
-      <c r="R81" t="s">
-        <v>35</v>
-      </c>
-      <c r="S81" t="s">
-        <v>44</v>
-      </c>
-      <c r="T81" t="s">
-        <v>83</v>
-      </c>
-      <c r="U81" t="s">
-        <v>31</v>
-      </c>
-      <c r="X81">
+      <c r="P81" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" t="s">
+        <v>40</v>
+      </c>
+      <c r="X81" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB81">
         <v>5</v>
       </c>
     </row>
@@ -4149,7 +4377,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -4161,15 +4389,15 @@
         <v>-40</v>
       </c>
       <c r="G82" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H82" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I82" t="s">
-        <v>29</v>
-      </c>
-      <c r="X82">
+        <v>33</v>
+      </c>
+      <c r="AB82">
         <v>5</v>
       </c>
     </row>
@@ -4181,7 +4409,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4193,39 +4421,42 @@
         <v>-28</v>
       </c>
       <c r="G83" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H83" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I83" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J83">
         <v>-2</v>
       </c>
       <c r="K83" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L83">
         <v>7</v>
       </c>
       <c r="M83" t="s">
-        <v>41</v>
-      </c>
-      <c r="R83" t="s">
-        <v>35</v>
-      </c>
-      <c r="S83" t="s">
-        <v>49</v>
-      </c>
-      <c r="T83" t="s">
-        <v>94</v>
-      </c>
-      <c r="U83" t="s">
-        <v>35</v>
-      </c>
-      <c r="X83">
+        <v>47</v>
+      </c>
+      <c r="P83" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" t="s">
+        <v>40</v>
+      </c>
+      <c r="X83" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB83">
         <v>6</v>
       </c>
     </row>
@@ -4237,7 +4468,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4249,39 +4480,42 @@
         <v>-26</v>
       </c>
       <c r="G84" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H84" t="s">
+        <v>44</v>
+      </c>
+      <c r="I84" t="s">
+        <v>45</v>
+      </c>
+      <c r="J84">
+        <v>2</v>
+      </c>
+      <c r="K84" t="s">
         <v>38</v>
-      </c>
-      <c r="I84" t="s">
-        <v>39</v>
-      </c>
-      <c r="J84">
-        <v>2</v>
-      </c>
-      <c r="K84" t="s">
-        <v>34</v>
       </c>
       <c r="L84">
         <v>7</v>
       </c>
       <c r="M84" t="s">
-        <v>45</v>
-      </c>
-      <c r="R84" t="s">
-        <v>35</v>
-      </c>
-      <c r="S84" t="s">
-        <v>61</v>
-      </c>
-      <c r="T84" t="s">
-        <v>95</v>
-      </c>
-      <c r="U84" t="s">
-        <v>31</v>
-      </c>
-      <c r="X84">
+        <v>53</v>
+      </c>
+      <c r="P84" t="s">
+        <v>66</v>
+      </c>
+      <c r="W84" t="s">
+        <v>40</v>
+      </c>
+      <c r="X84" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB84">
         <v>6</v>
       </c>
     </row>
@@ -4293,7 +4527,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -4305,19 +4539,19 @@
         <v>-28</v>
       </c>
       <c r="G85" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H85" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I85" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L85">
         <v>6</v>
@@ -4328,19 +4562,22 @@
       <c r="O85">
         <v>1</v>
       </c>
-      <c r="R85" t="s">
-        <v>31</v>
-      </c>
-      <c r="S85" t="s">
-        <v>61</v>
-      </c>
-      <c r="T85" t="s">
-        <v>62</v>
-      </c>
-      <c r="U85" t="s">
-        <v>31</v>
-      </c>
-      <c r="X85">
+      <c r="P85" t="s">
+        <v>66</v>
+      </c>
+      <c r="W85" t="s">
+        <v>35</v>
+      </c>
+      <c r="X85" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB85">
         <v>6</v>
       </c>
     </row>
@@ -4352,7 +4589,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -4364,15 +4601,15 @@
         <v>-28</v>
       </c>
       <c r="G86" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H86" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I86" t="s">
-        <v>29</v>
-      </c>
-      <c r="X86">
+        <v>33</v>
+      </c>
+      <c r="AB86">
         <v>6</v>
       </c>
     </row>
@@ -4384,7 +4621,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4396,36 +4633,39 @@
         <v>-38</v>
       </c>
       <c r="G87" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H87" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I87" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J87">
         <v>-3</v>
       </c>
       <c r="K87" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L87">
         <v>7</v>
       </c>
       <c r="M87" t="s">
-        <v>41</v>
-      </c>
-      <c r="R87" t="s">
-        <v>43</v>
-      </c>
-      <c r="S87" t="s">
-        <v>44</v>
-      </c>
-      <c r="U87" t="s">
-        <v>31</v>
-      </c>
-      <c r="X87">
+        <v>47</v>
+      </c>
+      <c r="P87" t="s">
+        <v>50</v>
+      </c>
+      <c r="W87" t="s">
+        <v>51</v>
+      </c>
+      <c r="X87" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB87">
         <v>6</v>
       </c>
     </row>
@@ -4437,7 +4677,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -4449,33 +4689,36 @@
         <v>-35</v>
       </c>
       <c r="G88" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H88" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I88" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J88">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L88">
         <v>6</v>
       </c>
       <c r="M88" t="s">
-        <v>45</v>
-      </c>
-      <c r="R88" t="s">
-        <v>31</v>
-      </c>
-      <c r="U88" t="s">
-        <v>35</v>
-      </c>
-      <c r="X88">
+        <v>53</v>
+      </c>
+      <c r="P88" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB88">
         <v>6</v>
       </c>
     </row>
@@ -4487,7 +4730,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D89">
         <v>3</v>
@@ -4499,19 +4742,19 @@
         <v>-36</v>
       </c>
       <c r="G89" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H89" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I89" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J89">
         <v>11</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L89">
         <v>7</v>
@@ -4522,16 +4765,19 @@
       <c r="O89">
         <v>4</v>
       </c>
-      <c r="R89" t="s">
-        <v>31</v>
-      </c>
-      <c r="S89" t="s">
-        <v>85</v>
-      </c>
-      <c r="U89" t="s">
-        <v>31</v>
-      </c>
-      <c r="X89">
+      <c r="P89" t="s">
+        <v>49</v>
+      </c>
+      <c r="W89" t="s">
+        <v>35</v>
+      </c>
+      <c r="X89" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB89">
         <v>6</v>
       </c>
     </row>
@@ -4543,7 +4789,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D90">
         <v>4</v>
@@ -4555,36 +4801,39 @@
         <v>-47</v>
       </c>
       <c r="G90" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H90" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I90" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L90">
         <v>7</v>
       </c>
       <c r="M90" t="s">
-        <v>45</v>
-      </c>
-      <c r="R90" t="s">
-        <v>35</v>
-      </c>
-      <c r="S90" t="s">
-        <v>70</v>
-      </c>
-      <c r="U90" t="s">
-        <v>35</v>
-      </c>
-      <c r="X90">
+        <v>53</v>
+      </c>
+      <c r="P90" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" t="s">
+        <v>40</v>
+      </c>
+      <c r="X90" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB90">
         <v>6</v>
       </c>
     </row>
@@ -4596,7 +4845,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4608,39 +4857,42 @@
         <v>47</v>
       </c>
       <c r="G91" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H91" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I91" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J91">
         <v>6</v>
       </c>
       <c r="K91" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L91">
         <v>7</v>
       </c>
       <c r="M91" t="s">
-        <v>41</v>
-      </c>
-      <c r="R91" t="s">
-        <v>35</v>
-      </c>
-      <c r="S91" t="s">
-        <v>59</v>
-      </c>
-      <c r="T91" t="s">
-        <v>96</v>
-      </c>
-      <c r="U91" t="s">
-        <v>35</v>
-      </c>
-      <c r="X91">
+        <v>47</v>
+      </c>
+      <c r="P91" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" t="s">
+        <v>40</v>
+      </c>
+      <c r="X91" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB91">
         <v>7</v>
       </c>
     </row>
@@ -4652,7 +4904,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -4664,39 +4916,42 @@
         <v>41</v>
       </c>
       <c r="G92" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H92" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I92" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J92">
         <v>7</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L92">
         <v>6</v>
       </c>
       <c r="M92" t="s">
-        <v>41</v>
-      </c>
-      <c r="R92" t="s">
-        <v>31</v>
-      </c>
-      <c r="S92" t="s">
-        <v>57</v>
-      </c>
-      <c r="T92" t="s">
-        <v>97</v>
-      </c>
-      <c r="U92" t="s">
-        <v>35</v>
-      </c>
-      <c r="X92">
+        <v>47</v>
+      </c>
+      <c r="P92" t="s">
+        <v>89</v>
+      </c>
+      <c r="W92" t="s">
+        <v>35</v>
+      </c>
+      <c r="X92" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB92">
         <v>7</v>
       </c>
     </row>
@@ -4708,7 +4963,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4720,19 +4975,19 @@
         <v>34</v>
       </c>
       <c r="G93" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H93" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I93" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J93">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L93">
         <v>6</v>
@@ -4743,19 +4998,22 @@
       <c r="O93">
         <v>2</v>
       </c>
-      <c r="R93" t="s">
-        <v>31</v>
-      </c>
-      <c r="S93" t="s">
-        <v>44</v>
-      </c>
-      <c r="T93" t="s">
-        <v>83</v>
-      </c>
-      <c r="U93" t="s">
-        <v>31</v>
-      </c>
-      <c r="X93">
+      <c r="P93" t="s">
+        <v>30</v>
+      </c>
+      <c r="W93" t="s">
+        <v>35</v>
+      </c>
+      <c r="X93" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB93">
         <v>7</v>
       </c>
     </row>
@@ -4767,7 +5025,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -4779,39 +5037,42 @@
         <v>33</v>
       </c>
       <c r="G94" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H94" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I94" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L94">
         <v>7</v>
       </c>
       <c r="M94" t="s">
-        <v>64</v>
-      </c>
-      <c r="R94" t="s">
-        <v>35</v>
-      </c>
-      <c r="S94" t="s">
-        <v>49</v>
-      </c>
-      <c r="T94" t="s">
-        <v>98</v>
-      </c>
-      <c r="U94" t="s">
-        <v>35</v>
-      </c>
-      <c r="X94">
+        <v>74</v>
+      </c>
+      <c r="P94" t="s">
+        <v>30</v>
+      </c>
+      <c r="W94" t="s">
+        <v>40</v>
+      </c>
+      <c r="X94" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB94">
         <v>7</v>
       </c>
     </row>
@@ -4823,7 +5084,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -4835,19 +5096,19 @@
         <v>33</v>
       </c>
       <c r="G95" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H95" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I95" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J95">
         <v>14</v>
       </c>
       <c r="K95" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L95">
         <v>4</v>
@@ -4858,19 +5119,22 @@
       <c r="O95">
         <v>2</v>
       </c>
-      <c r="R95" t="s">
-        <v>31</v>
-      </c>
-      <c r="S95" t="s">
-        <v>36</v>
-      </c>
-      <c r="T95" t="s">
-        <v>63</v>
-      </c>
-      <c r="U95" t="s">
-        <v>31</v>
-      </c>
-      <c r="X95">
+      <c r="P95" t="s">
+        <v>30</v>
+      </c>
+      <c r="W95" t="s">
+        <v>35</v>
+      </c>
+      <c r="X95" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB95">
         <v>7</v>
       </c>
     </row>
@@ -4882,7 +5146,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -4894,36 +5158,39 @@
         <v>19</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H96" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I96" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="J96">
         <v>-6</v>
       </c>
       <c r="K96" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L96">
         <v>6</v>
       </c>
-      <c r="R96" t="s">
-        <v>35</v>
-      </c>
-      <c r="S96" t="s">
-        <v>44</v>
-      </c>
-      <c r="T96" t="s">
-        <v>100</v>
-      </c>
-      <c r="U96" t="s">
-        <v>31</v>
-      </c>
-      <c r="X96">
+      <c r="P96" t="s">
+        <v>30</v>
+      </c>
+      <c r="W96" t="s">
+        <v>40</v>
+      </c>
+      <c r="X96" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB96">
         <v>7</v>
       </c>
     </row>
@@ -4935,7 +5202,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -4947,19 +5214,19 @@
         <v>-24</v>
       </c>
       <c r="G97" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H97" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I97" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J97">
         <v>4</v>
       </c>
       <c r="K97" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L97">
         <v>6</v>
@@ -4970,13 +5237,16 @@
       <c r="O97">
         <v>3</v>
       </c>
-      <c r="R97" t="s">
-        <v>35</v>
-      </c>
-      <c r="U97" t="s">
-        <v>35</v>
-      </c>
-      <c r="X97">
+      <c r="P97" t="s">
+        <v>49</v>
+      </c>
+      <c r="W97" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB97">
         <v>7</v>
       </c>
     </row>
@@ -4988,7 +5258,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5000,19 +5270,19 @@
         <v>-28</v>
       </c>
       <c r="G98" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H98" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I98" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J98">
         <v>3</v>
       </c>
       <c r="K98" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L98">
         <v>7</v>
@@ -5023,13 +5293,16 @@
       <c r="O98">
         <v>3</v>
       </c>
-      <c r="R98" t="s">
-        <v>43</v>
-      </c>
-      <c r="U98" t="s">
-        <v>35</v>
-      </c>
-      <c r="X98">
+      <c r="P98" t="s">
+        <v>50</v>
+      </c>
+      <c r="W98" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB98">
         <v>7</v>
       </c>
     </row>
@@ -5041,7 +5314,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -5053,36 +5326,39 @@
         <v>-31</v>
       </c>
       <c r="G99" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H99" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I99" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J99">
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L99">
         <v>7</v>
       </c>
       <c r="M99" t="s">
-        <v>56</v>
-      </c>
-      <c r="R99" t="s">
-        <v>31</v>
-      </c>
-      <c r="S99" t="s">
-        <v>85</v>
-      </c>
-      <c r="U99" t="s">
-        <v>35</v>
-      </c>
-      <c r="X99">
+        <v>65</v>
+      </c>
+      <c r="P99" t="s">
+        <v>30</v>
+      </c>
+      <c r="W99" t="s">
+        <v>35</v>
+      </c>
+      <c r="X99" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB99">
         <v>7</v>
       </c>
     </row>
@@ -5094,7 +5370,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D100">
         <v>4</v>
@@ -5106,15 +5382,15 @@
         <v>-33</v>
       </c>
       <c r="G100" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H100" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I100" t="s">
-        <v>87</v>
-      </c>
-      <c r="X100">
+        <v>99</v>
+      </c>
+      <c r="AB100">
         <v>7</v>
       </c>
     </row>
@@ -5126,7 +5402,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -5138,39 +5414,42 @@
         <v>-33</v>
       </c>
       <c r="G101" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H101" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I101" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J101">
         <v>-1</v>
       </c>
       <c r="K101" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L101">
         <v>7</v>
       </c>
       <c r="M101" t="s">
-        <v>56</v>
-      </c>
-      <c r="R101" t="s">
-        <v>35</v>
-      </c>
-      <c r="S101" t="s">
-        <v>59</v>
-      </c>
-      <c r="T101" t="s">
-        <v>102</v>
-      </c>
-      <c r="U101" t="s">
-        <v>31</v>
-      </c>
-      <c r="X101">
+        <v>65</v>
+      </c>
+      <c r="P101" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" t="s">
+        <v>40</v>
+      </c>
+      <c r="X101" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB101">
         <v>8</v>
       </c>
     </row>
@@ -5182,7 +5461,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -5194,19 +5473,19 @@
         <v>-32</v>
       </c>
       <c r="G102" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H102" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I102" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L102">
         <v>6</v>
@@ -5217,19 +5496,22 @@
       <c r="O102">
         <v>2</v>
       </c>
-      <c r="R102" t="s">
-        <v>35</v>
-      </c>
-      <c r="S102" t="s">
-        <v>44</v>
-      </c>
-      <c r="T102" t="s">
-        <v>67</v>
-      </c>
-      <c r="U102" t="s">
-        <v>35</v>
-      </c>
-      <c r="X102">
+      <c r="P102" t="s">
+        <v>49</v>
+      </c>
+      <c r="W102" t="s">
+        <v>40</v>
+      </c>
+      <c r="X102" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB102">
         <v>8</v>
       </c>
     </row>
@@ -5241,7 +5523,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D103">
         <v>3</v>
@@ -5253,21 +5535,24 @@
         <v>-32</v>
       </c>
       <c r="G103" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I103" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J103">
         <v>-5</v>
       </c>
       <c r="K103" t="s">
-        <v>34</v>
-      </c>
-      <c r="S103" t="s">
-        <v>44</v>
-      </c>
-      <c r="X103">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
+        <v>43</v>
+      </c>
+      <c r="X103" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB103">
         <v>8</v>
       </c>
     </row>
@@ -5279,7 +5564,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D104">
         <v>3</v>
@@ -5291,19 +5576,19 @@
         <v>-27</v>
       </c>
       <c r="G104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H104" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I104" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J104">
         <v>53</v>
       </c>
       <c r="K104" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L104">
         <v>5</v>
@@ -5314,19 +5599,22 @@
       <c r="O104">
         <v>7</v>
       </c>
-      <c r="R104" t="s">
-        <v>35</v>
-      </c>
-      <c r="S104" t="s">
-        <v>36</v>
-      </c>
-      <c r="T104" t="s">
-        <v>103</v>
-      </c>
-      <c r="U104" t="s">
-        <v>31</v>
-      </c>
-      <c r="X104">
+      <c r="P104" t="s">
+        <v>49</v>
+      </c>
+      <c r="W104" t="s">
+        <v>40</v>
+      </c>
+      <c r="X104" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB104">
         <v>8</v>
       </c>
     </row>
@@ -5338,7 +5626,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -5350,19 +5638,19 @@
         <v>20</v>
       </c>
       <c r="G105" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H105" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I105" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J105">
         <v>20</v>
       </c>
       <c r="K105" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L105">
         <v>7</v>
@@ -5373,22 +5661,25 @@
       <c r="O105">
         <v>7</v>
       </c>
-      <c r="R105" t="s">
-        <v>35</v>
-      </c>
-      <c r="S105" t="s">
-        <v>44</v>
-      </c>
-      <c r="T105" t="s">
-        <v>103</v>
-      </c>
-      <c r="U105" t="s">
-        <v>31</v>
-      </c>
-      <c r="V105" t="s">
-        <v>35</v>
-      </c>
-      <c r="X105">
+      <c r="P105" t="s">
+        <v>43</v>
+      </c>
+      <c r="W105" t="s">
+        <v>40</v>
+      </c>
+      <c r="X105" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB105">
         <v>8</v>
       </c>
     </row>
@@ -5400,7 +5691,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -5409,15 +5700,15 @@
         <v>3</v>
       </c>
       <c r="G106" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H106" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I106" t="s">
-        <v>92</v>
-      </c>
-      <c r="X106">
+        <v>105</v>
+      </c>
+      <c r="AB106">
         <v>8</v>
       </c>
     </row>
@@ -5429,7 +5720,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -5438,15 +5729,15 @@
         <v>-40</v>
       </c>
       <c r="G107" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H107" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I107" t="s">
-        <v>29</v>
-      </c>
-      <c r="X107">
+        <v>33</v>
+      </c>
+      <c r="AB107">
         <v>9</v>
       </c>
     </row>
@@ -5458,7 +5749,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5470,19 +5761,19 @@
         <v>-46</v>
       </c>
       <c r="G108" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H108" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I108" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J108">
         <v>6</v>
       </c>
       <c r="K108" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L108">
         <v>7</v>
@@ -5493,13 +5784,16 @@
       <c r="O108">
         <v>1</v>
       </c>
-      <c r="R108" t="s">
-        <v>31</v>
-      </c>
-      <c r="U108" t="s">
-        <v>31</v>
-      </c>
-      <c r="X108">
+      <c r="P108" t="s">
+        <v>49</v>
+      </c>
+      <c r="W108" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB108">
         <v>8</v>
       </c>
     </row>
@@ -5511,7 +5805,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -5523,33 +5817,36 @@
         <v>48</v>
       </c>
       <c r="G109" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H109" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I109" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J109">
         <v>-1</v>
       </c>
       <c r="K109" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L109">
         <v>7</v>
       </c>
       <c r="M109" t="s">
-        <v>45</v>
-      </c>
-      <c r="R109" t="s">
-        <v>35</v>
-      </c>
-      <c r="U109" t="s">
-        <v>35</v>
-      </c>
-      <c r="X109">
+        <v>53</v>
+      </c>
+      <c r="P109" t="s">
+        <v>43</v>
+      </c>
+      <c r="W109" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB109">
         <v>8</v>
       </c>
     </row>
@@ -5561,7 +5858,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -5573,19 +5870,19 @@
         <v>49</v>
       </c>
       <c r="G110" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H110" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I110" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J110">
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L110">
         <v>6</v>
@@ -5596,13 +5893,16 @@
       <c r="O110">
         <v>7</v>
       </c>
-      <c r="R110" t="s">
-        <v>43</v>
-      </c>
-      <c r="U110" t="s">
-        <v>31</v>
-      </c>
-      <c r="X110">
+      <c r="P110" t="s">
+        <v>50</v>
+      </c>
+      <c r="W110" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB110">
         <v>8</v>
       </c>
     </row>
@@ -5614,7 +5914,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D111">
         <v>4</v>
@@ -5626,15 +5926,15 @@
         <v>49</v>
       </c>
       <c r="G111" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H111" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I111" t="s">
-        <v>91</v>
-      </c>
-      <c r="X111">
+        <v>104</v>
+      </c>
+      <c r="AB111">
         <v>8</v>
       </c>
     </row>
@@ -5646,7 +5946,7 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5658,42 +5958,45 @@
         <v>-14</v>
       </c>
       <c r="G112" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H112" t="s">
+        <v>44</v>
+      </c>
+      <c r="I112" t="s">
+        <v>45</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112" t="s">
         <v>38</v>
-      </c>
-      <c r="I112" t="s">
-        <v>39</v>
-      </c>
-      <c r="J112">
-        <v>1</v>
-      </c>
-      <c r="K112" t="s">
-        <v>34</v>
       </c>
       <c r="L112">
         <v>7</v>
       </c>
       <c r="M112" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q112">
+        <v>65</v>
+      </c>
+      <c r="P112" t="s">
+        <v>66</v>
+      </c>
+      <c r="V112">
         <v>0</v>
       </c>
-      <c r="R112" t="s">
-        <v>31</v>
-      </c>
-      <c r="S112" t="s">
-        <v>57</v>
-      </c>
-      <c r="T112" t="s">
-        <v>58</v>
-      </c>
-      <c r="U112" t="s">
-        <v>31</v>
-      </c>
-      <c r="X112">
+      <c r="W112" t="s">
+        <v>35</v>
+      </c>
+      <c r="X112" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB112">
         <v>9</v>
       </c>
     </row>
@@ -5705,7 +6008,7 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5717,19 +6020,19 @@
         <v>-15</v>
       </c>
       <c r="G113" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H113" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I113" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L113">
         <v>7</v>
@@ -5740,19 +6043,22 @@
       <c r="O113">
         <v>3</v>
       </c>
-      <c r="R113" t="s">
-        <v>35</v>
-      </c>
-      <c r="S113" t="s">
-        <v>44</v>
-      </c>
-      <c r="T113" t="s">
-        <v>63</v>
-      </c>
-      <c r="U113" t="s">
-        <v>35</v>
-      </c>
-      <c r="X113">
+      <c r="P113" t="s">
+        <v>43</v>
+      </c>
+      <c r="W113" t="s">
+        <v>40</v>
+      </c>
+      <c r="X113" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB113">
         <v>9</v>
       </c>
     </row>
@@ -5764,7 +6070,7 @@
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -5776,36 +6082,39 @@
         <v>-15</v>
       </c>
       <c r="G114" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H114" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I114" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J114">
         <v>-10</v>
       </c>
       <c r="K114" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L114">
         <v>6</v>
       </c>
-      <c r="R114" t="s">
-        <v>35</v>
-      </c>
-      <c r="S114" t="s">
-        <v>84</v>
-      </c>
-      <c r="T114" t="s">
-        <v>100</v>
-      </c>
-      <c r="U114" t="s">
-        <v>35</v>
-      </c>
-      <c r="X114">
+      <c r="P114" t="s">
+        <v>43</v>
+      </c>
+      <c r="W114" t="s">
+        <v>40</v>
+      </c>
+      <c r="X114" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB114">
         <v>9</v>
       </c>
     </row>
@@ -5817,7 +6126,7 @@
         <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D115">
         <v>4</v>
@@ -5829,18 +6138,18 @@
         <v>-5</v>
       </c>
       <c r="G115" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H115" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I115" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="J115">
         <v>-5</v>
       </c>
-      <c r="X115">
+      <c r="AB115">
         <v>9</v>
       </c>
     </row>
@@ -5852,19 +6161,19 @@
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F116">
         <v>-20</v>
       </c>
       <c r="G116" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H116" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I116" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="117">
@@ -5875,7 +6184,7 @@
         <v>3</v>
       </c>
       <c r="C117" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -5887,36 +6196,39 @@
         <v>-44</v>
       </c>
       <c r="G117" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H117" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I117" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L117">
         <v>6</v>
       </c>
       <c r="M117" t="s">
-        <v>45</v>
-      </c>
-      <c r="R117" t="s">
-        <v>31</v>
-      </c>
-      <c r="S117" t="s">
-        <v>84</v>
-      </c>
-      <c r="U117" t="s">
-        <v>31</v>
-      </c>
-      <c r="X117">
+        <v>53</v>
+      </c>
+      <c r="P117" t="s">
+        <v>49</v>
+      </c>
+      <c r="W117" t="s">
+        <v>35</v>
+      </c>
+      <c r="X117" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB117">
         <v>9</v>
       </c>
     </row>
@@ -5928,7 +6240,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D118">
         <v>2</v>
@@ -5940,19 +6252,19 @@
         <v>-44</v>
       </c>
       <c r="G118" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H118" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I118" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J118">
         <v>13</v>
       </c>
       <c r="K118" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L118">
         <v>8</v>
@@ -5963,16 +6275,19 @@
       <c r="O118">
         <v>1</v>
       </c>
-      <c r="R118" t="s">
-        <v>31</v>
-      </c>
-      <c r="S118" t="s">
-        <v>77</v>
-      </c>
-      <c r="U118" t="s">
-        <v>31</v>
-      </c>
-      <c r="X118">
+      <c r="P118" t="s">
+        <v>43</v>
+      </c>
+      <c r="W118" t="s">
+        <v>35</v>
+      </c>
+      <c r="X118" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB118">
         <v>9</v>
       </c>
     </row>
@@ -5984,7 +6299,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -5996,19 +6311,19 @@
         <v>43</v>
       </c>
       <c r="G119" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H119" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I119" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J119">
         <v>20</v>
       </c>
       <c r="K119" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L119">
         <v>7</v>
@@ -6019,13 +6334,16 @@
       <c r="O119">
         <v>1</v>
       </c>
-      <c r="R119" t="s">
-        <v>35</v>
-      </c>
-      <c r="U119" t="s">
-        <v>31</v>
-      </c>
-      <c r="X119">
+      <c r="P119" t="s">
+        <v>49</v>
+      </c>
+      <c r="W119" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB119">
         <v>9</v>
       </c>
     </row>
@@ -6037,7 +6355,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -6049,39 +6367,42 @@
         <v>23</v>
       </c>
       <c r="G120" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H120" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I120" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J120">
         <v>-2</v>
       </c>
       <c r="K120" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L120">
         <v>6</v>
       </c>
       <c r="M120" t="s">
-        <v>45</v>
-      </c>
-      <c r="R120" t="s">
-        <v>35</v>
-      </c>
-      <c r="S120" t="s">
-        <v>106</v>
-      </c>
-      <c r="U120" t="s">
-        <v>35</v>
-      </c>
-      <c r="V120" t="s">
-        <v>35</v>
-      </c>
-      <c r="X120">
+        <v>53</v>
+      </c>
+      <c r="P120" t="s">
+        <v>49</v>
+      </c>
+      <c r="W120" t="s">
+        <v>40</v>
+      </c>
+      <c r="X120" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA120" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB120">
         <v>9</v>
       </c>
     </row>
@@ -6093,7 +6414,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -6105,19 +6426,19 @@
         <v>25</v>
       </c>
       <c r="G121" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H121" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I121" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L121">
         <v>6</v>
@@ -6128,13 +6449,16 @@
       <c r="O121">
         <v>7</v>
       </c>
-      <c r="R121" t="s">
-        <v>35</v>
-      </c>
-      <c r="U121" t="s">
-        <v>31</v>
-      </c>
-      <c r="X121">
+      <c r="P121" t="s">
+        <v>49</v>
+      </c>
+      <c r="W121" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB121">
         <v>9</v>
       </c>
     </row>
@@ -6146,7 +6470,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D122">
         <v>3</v>
@@ -6158,19 +6482,19 @@
         <v>25</v>
       </c>
       <c r="G122" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H122" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I122" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J122">
         <v>17</v>
       </c>
       <c r="K122" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L122">
         <v>7</v>
@@ -6181,16 +6505,19 @@
       <c r="O122">
         <v>2</v>
       </c>
-      <c r="R122" t="s">
-        <v>35</v>
-      </c>
-      <c r="S122" t="s">
-        <v>85</v>
-      </c>
-      <c r="U122" t="s">
-        <v>35</v>
-      </c>
-      <c r="X122">
+      <c r="P122" t="s">
+        <v>49</v>
+      </c>
+      <c r="W122" t="s">
+        <v>40</v>
+      </c>
+      <c r="X122" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB122">
         <v>9</v>
       </c>
     </row>
@@ -6202,7 +6529,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -6214,36 +6541,39 @@
         <v>8</v>
       </c>
       <c r="G123" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H123" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I123" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J123">
         <v>-1</v>
       </c>
       <c r="K123" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L123">
         <v>7</v>
       </c>
       <c r="M123" t="s">
-        <v>41</v>
-      </c>
-      <c r="R123" t="s">
-        <v>35</v>
-      </c>
-      <c r="S123" t="s">
-        <v>77</v>
-      </c>
-      <c r="U123" t="s">
-        <v>31</v>
-      </c>
-      <c r="X123">
+        <v>47</v>
+      </c>
+      <c r="P123" t="s">
+        <v>43</v>
+      </c>
+      <c r="W123" t="s">
+        <v>40</v>
+      </c>
+      <c r="X123" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB123">
         <v>9</v>
       </c>
     </row>
@@ -6255,7 +6585,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -6267,30 +6597,33 @@
         <v>9</v>
       </c>
       <c r="G124" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H124" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I124" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J124">
         <v>-15</v>
       </c>
       <c r="K124" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L124">
         <v>6</v>
       </c>
-      <c r="R124" t="s">
-        <v>43</v>
-      </c>
-      <c r="U124" t="s">
-        <v>35</v>
-      </c>
-      <c r="X124">
+      <c r="P124" t="s">
+        <v>50</v>
+      </c>
+      <c r="W124" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB124">
         <v>9</v>
       </c>
     </row>
@@ -6302,7 +6635,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126">
@@ -6313,7 +6646,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D126">
         <v>2</v>
@@ -6325,33 +6658,36 @@
         <v>24</v>
       </c>
       <c r="G126" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H126" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I126" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J126">
         <v>-4</v>
       </c>
       <c r="K126" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L126">
         <v>7</v>
       </c>
       <c r="M126" t="s">
-        <v>64</v>
-      </c>
-      <c r="R126" t="s">
-        <v>31</v>
-      </c>
-      <c r="U126" t="s">
-        <v>35</v>
-      </c>
-      <c r="X126">
+        <v>74</v>
+      </c>
+      <c r="P126" t="s">
+        <v>30</v>
+      </c>
+      <c r="W126" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB126">
         <v>9</v>
       </c>
     </row>
@@ -6363,7 +6699,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D127">
         <v>3</v>
@@ -6375,18 +6711,18 @@
         <v>28</v>
       </c>
       <c r="G127" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I127" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>40</v>
-      </c>
-      <c r="X127">
+        <v>46</v>
+      </c>
+      <c r="AB127">
         <v>9</v>
       </c>
     </row>
@@ -6398,7 +6734,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D128">
         <v>3</v>
@@ -6410,19 +6746,19 @@
         <v>28</v>
       </c>
       <c r="G128" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H128" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I128" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J128">
         <v>-10</v>
       </c>
       <c r="K128" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L128">
         <v>7</v>
@@ -6433,16 +6769,19 @@
       <c r="O128">
         <v>3</v>
       </c>
-      <c r="R128" t="s">
-        <v>35</v>
-      </c>
-      <c r="S128" t="s">
-        <v>84</v>
-      </c>
-      <c r="U128" t="s">
-        <v>35</v>
-      </c>
-      <c r="X128">
+      <c r="P128" t="s">
+        <v>30</v>
+      </c>
+      <c r="W128" t="s">
+        <v>40</v>
+      </c>
+      <c r="X128" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB128">
         <v>9</v>
       </c>
     </row>
@@ -6454,7 +6793,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D129">
         <v>3</v>
@@ -6466,19 +6805,19 @@
         <v>38</v>
       </c>
       <c r="G129" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H129" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I129" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L129">
         <v>6</v>
@@ -6489,16 +6828,19 @@
       <c r="O129">
         <v>6</v>
       </c>
-      <c r="R129" t="s">
-        <v>43</v>
-      </c>
-      <c r="S129" t="s">
-        <v>44</v>
-      </c>
-      <c r="U129" t="s">
-        <v>35</v>
-      </c>
-      <c r="X129">
+      <c r="P129" t="s">
+        <v>50</v>
+      </c>
+      <c r="W129" t="s">
+        <v>51</v>
+      </c>
+      <c r="X129" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB129">
         <v>9</v>
       </c>
     </row>
@@ -6510,7 +6852,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D130">
         <v>4</v>
@@ -6522,15 +6864,15 @@
         <v>38</v>
       </c>
       <c r="G130" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H130" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I130" t="s">
-        <v>108</v>
-      </c>
-      <c r="X130">
+        <v>121</v>
+      </c>
+      <c r="AB130">
         <v>9</v>
       </c>
     </row>
@@ -6542,7 +6884,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -6554,19 +6896,19 @@
         <v>-11</v>
       </c>
       <c r="G131" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H131" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I131" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L131">
         <v>6</v>
@@ -6577,19 +6919,22 @@
       <c r="O131">
         <v>2</v>
       </c>
-      <c r="R131" t="s">
-        <v>35</v>
-      </c>
-      <c r="S131" t="s">
-        <v>36</v>
-      </c>
-      <c r="T131" t="s">
-        <v>93</v>
-      </c>
-      <c r="U131" t="s">
-        <v>35</v>
-      </c>
-      <c r="X131">
+      <c r="P131" t="s">
+        <v>43</v>
+      </c>
+      <c r="W131" t="s">
+        <v>40</v>
+      </c>
+      <c r="X131" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y131" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB131">
         <v>10</v>
       </c>
     </row>
@@ -6601,7 +6946,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D132">
         <v>2</v>
@@ -6613,19 +6958,19 @@
         <v>-11</v>
       </c>
       <c r="G132" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H132" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I132" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J132">
         <v>15</v>
       </c>
       <c r="K132" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L132">
         <v>7</v>
@@ -6636,19 +6981,22 @@
       <c r="O132">
         <v>1</v>
       </c>
-      <c r="R132" t="s">
-        <v>35</v>
-      </c>
-      <c r="S132" t="s">
-        <v>44</v>
-      </c>
-      <c r="T132" t="s">
-        <v>63</v>
-      </c>
-      <c r="U132" t="s">
-        <v>31</v>
-      </c>
-      <c r="X132">
+      <c r="P132" t="s">
+        <v>43</v>
+      </c>
+      <c r="W132" t="s">
+        <v>40</v>
+      </c>
+      <c r="X132" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB132">
         <v>10</v>
       </c>
     </row>
@@ -6660,7 +7008,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -6672,19 +7020,19 @@
         <v>-26</v>
       </c>
       <c r="G133" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H133" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I133" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J133">
         <v>10</v>
       </c>
       <c r="K133" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L133">
         <v>6</v>
@@ -6695,19 +7043,22 @@
       <c r="O133">
         <v>4</v>
       </c>
-      <c r="R133" t="s">
-        <v>35</v>
-      </c>
-      <c r="S133" t="s">
-        <v>36</v>
-      </c>
-      <c r="T133" t="s">
-        <v>63</v>
-      </c>
-      <c r="U133" t="s">
-        <v>31</v>
-      </c>
-      <c r="X133">
+      <c r="P133" t="s">
+        <v>49</v>
+      </c>
+      <c r="W133" t="s">
+        <v>40</v>
+      </c>
+      <c r="X133" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB133">
         <v>10</v>
       </c>
     </row>
@@ -6719,7 +7070,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -6731,19 +7082,19 @@
         <v>-36</v>
       </c>
       <c r="G134" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H134" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I134" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J134">
         <v>11</v>
       </c>
       <c r="K134" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L134">
         <v>6</v>
@@ -6754,19 +7105,22 @@
       <c r="O134">
         <v>4</v>
       </c>
-      <c r="R134" t="s">
-        <v>35</v>
-      </c>
-      <c r="S134" t="s">
-        <v>36</v>
-      </c>
-      <c r="T134" t="s">
-        <v>93</v>
-      </c>
-      <c r="U134" t="s">
-        <v>31</v>
-      </c>
-      <c r="X134">
+      <c r="P134" t="s">
+        <v>43</v>
+      </c>
+      <c r="W134" t="s">
+        <v>40</v>
+      </c>
+      <c r="X134" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB134">
         <v>10</v>
       </c>
     </row>
@@ -6778,7 +7132,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -6790,19 +7144,19 @@
         <v>-47</v>
       </c>
       <c r="G135" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H135" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I135" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J135">
         <v>5</v>
       </c>
       <c r="K135" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L135">
         <v>6</v>
@@ -6813,19 +7167,22 @@
       <c r="O135">
         <v>3</v>
       </c>
-      <c r="R135" t="s">
-        <v>35</v>
-      </c>
-      <c r="S135" t="s">
-        <v>36</v>
-      </c>
-      <c r="T135" t="s">
-        <v>109</v>
-      </c>
-      <c r="U135" t="s">
-        <v>35</v>
-      </c>
-      <c r="X135">
+      <c r="P135" t="s">
+        <v>43</v>
+      </c>
+      <c r="W135" t="s">
+        <v>40</v>
+      </c>
+      <c r="X135" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB135">
         <v>10</v>
       </c>
     </row>
@@ -6837,7 +7194,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -6849,19 +7206,19 @@
         <v>48</v>
       </c>
       <c r="G136" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H136" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I136" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L136">
         <v>6</v>
@@ -6872,19 +7229,22 @@
       <c r="O136">
         <v>3</v>
       </c>
-      <c r="R136" t="s">
-        <v>31</v>
-      </c>
-      <c r="S136" t="s">
-        <v>36</v>
-      </c>
-      <c r="T136" t="s">
-        <v>110</v>
-      </c>
-      <c r="U136" t="s">
-        <v>35</v>
-      </c>
-      <c r="X136">
+      <c r="P136" t="s">
+        <v>43</v>
+      </c>
+      <c r="W136" t="s">
+        <v>35</v>
+      </c>
+      <c r="X136" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB136">
         <v>10</v>
       </c>
     </row>
@@ -6896,7 +7256,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D137">
         <v>3</v>
@@ -6908,39 +7268,42 @@
         <v>48</v>
       </c>
       <c r="G137" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H137" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I137" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J137">
         <v>12</v>
       </c>
       <c r="K137" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L137">
         <v>6</v>
       </c>
       <c r="M137" t="s">
+        <v>47</v>
+      </c>
+      <c r="P137" t="s">
+        <v>30</v>
+      </c>
+      <c r="W137" t="s">
+        <v>35</v>
+      </c>
+      <c r="X137" t="s">
         <v>41</v>
       </c>
-      <c r="R137" t="s">
-        <v>31</v>
-      </c>
-      <c r="S137" t="s">
-        <v>36</v>
-      </c>
-      <c r="T137" t="s">
-        <v>72</v>
-      </c>
-      <c r="U137" t="s">
-        <v>31</v>
-      </c>
-      <c r="X137">
+      <c r="Y137" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB137">
         <v>10</v>
       </c>
     </row>
@@ -6952,7 +7315,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -6964,19 +7327,19 @@
         <v>36</v>
       </c>
       <c r="G138" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H138" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I138" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L138">
         <v>6</v>
@@ -6987,19 +7350,22 @@
       <c r="O138">
         <v>1</v>
       </c>
-      <c r="R138" t="s">
-        <v>31</v>
-      </c>
-      <c r="S138" t="s">
-        <v>36</v>
-      </c>
-      <c r="T138" t="s">
-        <v>82</v>
-      </c>
-      <c r="U138" t="s">
-        <v>31</v>
-      </c>
-      <c r="X138">
+      <c r="P138" t="s">
+        <v>43</v>
+      </c>
+      <c r="W138" t="s">
+        <v>35</v>
+      </c>
+      <c r="X138" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB138">
         <v>10</v>
       </c>
     </row>
@@ -7011,7 +7377,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D139">
         <v>2</v>
@@ -7023,19 +7389,19 @@
         <v>36</v>
       </c>
       <c r="G139" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H139" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I139" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J139">
         <v>7</v>
       </c>
       <c r="K139" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L139">
         <v>6</v>
@@ -7046,19 +7412,22 @@
       <c r="O139">
         <v>3</v>
       </c>
-      <c r="R139" t="s">
-        <v>31</v>
-      </c>
-      <c r="S139" t="s">
-        <v>44</v>
-      </c>
-      <c r="T139" t="s">
-        <v>83</v>
-      </c>
-      <c r="U139" t="s">
-        <v>35</v>
-      </c>
-      <c r="X139">
+      <c r="P139" t="s">
+        <v>30</v>
+      </c>
+      <c r="W139" t="s">
+        <v>35</v>
+      </c>
+      <c r="X139" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB139">
         <v>10</v>
       </c>
     </row>
@@ -7070,7 +7439,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D140">
         <v>3</v>
@@ -7082,39 +7451,42 @@
         <v>29</v>
       </c>
       <c r="G140" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H140" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I140" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J140">
         <v>-2</v>
       </c>
       <c r="K140" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L140">
         <v>7</v>
       </c>
       <c r="M140" t="s">
-        <v>41</v>
-      </c>
-      <c r="R140" t="s">
-        <v>35</v>
-      </c>
-      <c r="S140" t="s">
-        <v>57</v>
-      </c>
-      <c r="T140" t="s">
-        <v>58</v>
-      </c>
-      <c r="U140" t="s">
-        <v>31</v>
-      </c>
-      <c r="X140">
+        <v>47</v>
+      </c>
+      <c r="P140" t="s">
+        <v>89</v>
+      </c>
+      <c r="W140" t="s">
+        <v>40</v>
+      </c>
+      <c r="X140" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB140">
         <v>10</v>
       </c>
     </row>
@@ -7126,7 +7498,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D141">
         <v>4</v>
@@ -7138,19 +7510,19 @@
         <v>31</v>
       </c>
       <c r="G141" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H141" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I141" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L141">
         <v>7</v>
@@ -7161,19 +7533,22 @@
       <c r="O141">
         <v>5</v>
       </c>
-      <c r="R141" t="s">
-        <v>31</v>
-      </c>
-      <c r="S141" t="s">
-        <v>44</v>
-      </c>
-      <c r="T141" t="s">
-        <v>83</v>
-      </c>
-      <c r="U141" t="s">
-        <v>31</v>
-      </c>
-      <c r="X141">
+      <c r="P141" t="s">
+        <v>43</v>
+      </c>
+      <c r="W141" t="s">
+        <v>35</v>
+      </c>
+      <c r="X141" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB141">
         <v>10</v>
       </c>
     </row>
@@ -7185,7 +7560,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -7197,33 +7572,36 @@
         <v>-31</v>
       </c>
       <c r="G142" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H142" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I142" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J142">
         <v>3</v>
       </c>
       <c r="K142" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L142">
         <v>8</v>
       </c>
       <c r="M142" t="s">
-        <v>56</v>
-      </c>
-      <c r="R142" t="s">
-        <v>35</v>
-      </c>
-      <c r="U142" t="s">
-        <v>31</v>
-      </c>
-      <c r="X142">
+        <v>65</v>
+      </c>
+      <c r="P142" t="s">
+        <v>49</v>
+      </c>
+      <c r="W142" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB142">
         <v>10</v>
       </c>
     </row>
@@ -7235,7 +7613,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -7247,19 +7625,19 @@
         <v>-34</v>
       </c>
       <c r="G143" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H143" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I143" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J143">
         <v>7</v>
       </c>
       <c r="K143" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L143">
         <v>7</v>
@@ -7270,13 +7648,16 @@
       <c r="O143">
         <v>3</v>
       </c>
-      <c r="R143" t="s">
-        <v>43</v>
-      </c>
-      <c r="U143" t="s">
-        <v>35</v>
-      </c>
-      <c r="X143">
+      <c r="P143" t="s">
+        <v>50</v>
+      </c>
+      <c r="W143" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB143">
         <v>10</v>
       </c>
     </row>
@@ -7288,7 +7669,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -7300,36 +7681,39 @@
         <v>-41</v>
       </c>
       <c r="G144" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H144" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I144" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J144">
         <v>4</v>
       </c>
       <c r="K144" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L144">
         <v>8</v>
       </c>
       <c r="M144" t="s">
-        <v>45</v>
-      </c>
-      <c r="R144" t="s">
-        <v>35</v>
-      </c>
-      <c r="S144" t="s">
-        <v>84</v>
-      </c>
-      <c r="U144" t="s">
-        <v>35</v>
-      </c>
-      <c r="X144">
+        <v>53</v>
+      </c>
+      <c r="P144" t="s">
+        <v>43</v>
+      </c>
+      <c r="W144" t="s">
+        <v>40</v>
+      </c>
+      <c r="X144" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB144">
         <v>10</v>
       </c>
     </row>
@@ -7341,7 +7725,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D145">
         <v>2</v>
@@ -7353,36 +7737,39 @@
         <v>-45</v>
       </c>
       <c r="G145" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H145" t="s">
+        <v>44</v>
+      </c>
+      <c r="I145" t="s">
+        <v>45</v>
+      </c>
+      <c r="J145">
+        <v>35</v>
+      </c>
+      <c r="K145" t="s">
         <v>38</v>
-      </c>
-      <c r="I145" t="s">
-        <v>39</v>
-      </c>
-      <c r="J145">
-        <v>35</v>
-      </c>
-      <c r="K145" t="s">
-        <v>34</v>
       </c>
       <c r="L145">
         <v>7</v>
       </c>
       <c r="M145" t="s">
-        <v>45</v>
-      </c>
-      <c r="R145" t="s">
-        <v>31</v>
-      </c>
-      <c r="S145" t="s">
-        <v>84</v>
-      </c>
-      <c r="U145" t="s">
-        <v>31</v>
-      </c>
-      <c r="X145">
+        <v>53</v>
+      </c>
+      <c r="P145" t="s">
+        <v>30</v>
+      </c>
+      <c r="W145" t="s">
+        <v>35</v>
+      </c>
+      <c r="X145" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB145">
         <v>10</v>
       </c>
     </row>
@@ -7394,7 +7781,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -7406,36 +7793,39 @@
         <v>20</v>
       </c>
       <c r="G146" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H146" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I146" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J146">
         <v>4</v>
       </c>
       <c r="K146" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L146">
         <v>7</v>
       </c>
       <c r="M146" t="s">
-        <v>45</v>
-      </c>
-      <c r="R146" t="s">
-        <v>31</v>
-      </c>
-      <c r="S146" t="s">
-        <v>84</v>
-      </c>
-      <c r="U146" t="s">
-        <v>35</v>
-      </c>
-      <c r="X146">
+        <v>53</v>
+      </c>
+      <c r="P146" t="s">
+        <v>30</v>
+      </c>
+      <c r="W146" t="s">
+        <v>35</v>
+      </c>
+      <c r="X146" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z146" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB146">
         <v>10</v>
       </c>
     </row>
@@ -7447,7 +7837,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D147">
         <v>2</v>
@@ -7459,36 +7849,39 @@
         <v>16</v>
       </c>
       <c r="G147" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H147" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I147" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J147">
         <v>4</v>
       </c>
       <c r="K147" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L147">
         <v>7</v>
       </c>
       <c r="M147" t="s">
-        <v>45</v>
-      </c>
-      <c r="R147" t="s">
-        <v>35</v>
-      </c>
-      <c r="S147" t="s">
-        <v>84</v>
-      </c>
-      <c r="U147" t="s">
-        <v>35</v>
-      </c>
-      <c r="X147">
+        <v>53</v>
+      </c>
+      <c r="P147" t="s">
+        <v>30</v>
+      </c>
+      <c r="W147" t="s">
+        <v>40</v>
+      </c>
+      <c r="X147" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB147">
         <v>10</v>
       </c>
     </row>
@@ -7500,7 +7893,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149">
@@ -7511,7 +7904,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -7523,36 +7916,39 @@
         <v>12</v>
       </c>
       <c r="G149" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H149" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I149" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J149">
         <v>-8</v>
       </c>
       <c r="K149" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L149">
         <v>8</v>
       </c>
       <c r="M149" t="s">
-        <v>45</v>
-      </c>
-      <c r="R149" t="s">
-        <v>35</v>
-      </c>
-      <c r="S149" t="s">
-        <v>84</v>
-      </c>
-      <c r="U149" t="s">
-        <v>31</v>
-      </c>
-      <c r="X149">
+        <v>53</v>
+      </c>
+      <c r="P149" t="s">
+        <v>30</v>
+      </c>
+      <c r="W149" t="s">
+        <v>40</v>
+      </c>
+      <c r="X149" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB149">
         <v>10</v>
       </c>
     </row>
@@ -7564,7 +7960,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D150">
         <v>4</v>
@@ -7576,15 +7972,15 @@
         <v>20</v>
       </c>
       <c r="G150" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H150" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I150" t="s">
-        <v>51</v>
-      </c>
-      <c r="X150">
+        <v>59</v>
+      </c>
+      <c r="AB150">
         <v>10</v>
       </c>
     </row>
@@ -7596,21 +7992,21 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F151">
         <v>-40</v>
       </c>
       <c r="G151" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H151" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I151" t="s">
-        <v>29</v>
-      </c>
-      <c r="X151">
+        <v>33</v>
+      </c>
+      <c r="AB151">
         <v>10</v>
       </c>
     </row>
@@ -7622,7 +8018,7 @@
         <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -7634,19 +8030,19 @@
         <v>-47</v>
       </c>
       <c r="G152" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H152" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I152" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J152">
         <v>7</v>
       </c>
       <c r="K152" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L152">
         <v>6</v>
@@ -7657,19 +8053,22 @@
       <c r="O152">
         <v>3</v>
       </c>
-      <c r="R152" t="s">
-        <v>35</v>
-      </c>
-      <c r="S152" t="s">
-        <v>36</v>
-      </c>
-      <c r="T152" t="s">
-        <v>103</v>
-      </c>
-      <c r="U152" t="s">
-        <v>35</v>
-      </c>
-      <c r="X152">
+      <c r="P152" t="s">
+        <v>43</v>
+      </c>
+      <c r="W152" t="s">
+        <v>40</v>
+      </c>
+      <c r="X152" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y152" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z152" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB152">
         <v>11</v>
       </c>
     </row>
@@ -7681,7 +8080,7 @@
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D153">
         <v>2</v>
@@ -7693,19 +8092,19 @@
         <v>46</v>
       </c>
       <c r="G153" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H153" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I153" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L153">
         <v>5</v>
@@ -7716,19 +8115,22 @@
       <c r="O153">
         <v>6</v>
       </c>
-      <c r="R153" t="s">
-        <v>31</v>
-      </c>
-      <c r="S153" t="s">
-        <v>44</v>
-      </c>
-      <c r="T153" t="s">
-        <v>83</v>
-      </c>
-      <c r="U153" t="s">
-        <v>35</v>
-      </c>
-      <c r="X153">
+      <c r="P153" t="s">
+        <v>43</v>
+      </c>
+      <c r="W153" t="s">
+        <v>35</v>
+      </c>
+      <c r="X153" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y153" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z153" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB153">
         <v>11</v>
       </c>
     </row>
@@ -7740,7 +8142,7 @@
         <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -7752,19 +8154,19 @@
         <v>46</v>
       </c>
       <c r="G154" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H154" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I154" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J154">
         <v>7</v>
       </c>
       <c r="K154" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L154">
         <v>6</v>
@@ -7775,19 +8177,22 @@
       <c r="O154">
         <v>3</v>
       </c>
-      <c r="R154" t="s">
-        <v>31</v>
-      </c>
-      <c r="S154" t="s">
-        <v>36</v>
-      </c>
-      <c r="T154" t="s">
-        <v>82</v>
-      </c>
-      <c r="U154" t="s">
-        <v>35</v>
-      </c>
-      <c r="X154">
+      <c r="P154" t="s">
+        <v>43</v>
+      </c>
+      <c r="W154" t="s">
+        <v>35</v>
+      </c>
+      <c r="X154" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z154" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB154">
         <v>11</v>
       </c>
     </row>
@@ -7799,7 +8204,7 @@
         <v>4</v>
       </c>
       <c r="C155" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -7811,16 +8216,16 @@
         <v>39</v>
       </c>
       <c r="G155" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H155" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I155" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K155" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L155">
         <v>6</v>
@@ -7831,19 +8236,22 @@
       <c r="O155">
         <v>3</v>
       </c>
-      <c r="R155" t="s">
-        <v>31</v>
-      </c>
-      <c r="S155" t="s">
-        <v>36</v>
-      </c>
-      <c r="T155" t="s">
-        <v>110</v>
-      </c>
-      <c r="U155" t="s">
-        <v>35</v>
-      </c>
-      <c r="X155">
+      <c r="P155" t="s">
+        <v>43</v>
+      </c>
+      <c r="W155" t="s">
+        <v>35</v>
+      </c>
+      <c r="X155" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y155" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z155" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB155">
         <v>11</v>
       </c>
     </row>
